--- a/research/traditional_assets/database/data/kenya/kenya_tobacco.xlsx
+++ b/research/traditional_assets/database/data/kenya/kenya_tobacco.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1257257089323421</v>
+        <v>0.1253800318055451</v>
       </c>
       <c r="C2">
-        <v>290.2</v>
+        <v>288.0333827848179</v>
       </c>
       <c r="D2">
-        <v>290.2</v>
+        <v>290.9353827848179</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>2.902</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.902</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1451,28 +1451,28 @@
         <v>62.2</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1459706</v>
       </c>
       <c r="N2">
-        <v>62.2</v>
+        <v>62.0540294</v>
       </c>
       <c r="O2">
-        <v>18.66</v>
+        <v>18.61620882</v>
       </c>
       <c r="P2">
-        <v>43.54000000000001</v>
+        <v>43.43782058000001</v>
       </c>
       <c r="Q2">
-        <v>49.04000000000001</v>
+        <v>48.93782058000001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1257257089323421</v>
+        <v>0.1262908402076213</v>
       </c>
       <c r="T2">
-        <v>0.5572774141861078</v>
+        <v>0.5612177595389388</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>426.1132036177148</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1253800318055451</v>
+        <v>0.125034354678748</v>
       </c>
       <c r="C3">
-        <v>288.0333827848179</v>
+        <v>285.8705020390213</v>
       </c>
       <c r="D3">
-        <v>290.9353827848179</v>
+        <v>291.6745020390213</v>
       </c>
       <c r="E3">
-        <v>2.902</v>
+        <v>5.804</v>
       </c>
       <c r="F3">
-        <v>2.902</v>
+        <v>5.804</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1533,28 +1533,28 @@
         <v>62.2</v>
       </c>
       <c r="M3">
-        <v>0.1459706</v>
+        <v>0.2919412</v>
       </c>
       <c r="N3">
-        <v>62.0540294</v>
+        <v>61.90805880000001</v>
       </c>
       <c r="O3">
-        <v>18.61620882</v>
+        <v>18.57241764</v>
       </c>
       <c r="P3">
-        <v>43.43782058000001</v>
+        <v>43.33564116000001</v>
       </c>
       <c r="Q3">
-        <v>48.93782058000001</v>
+        <v>48.83564116000001</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1262908402076213</v>
+        <v>0.1268675047742327</v>
       </c>
       <c r="T3">
-        <v>0.5612177595389388</v>
+        <v>0.5652385201030521</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>426.1132036177148</v>
+        <v>213.0566018088574</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.125034354678748</v>
+        <v>0.124688677551951</v>
       </c>
       <c r="C4">
-        <v>285.8705020390213</v>
+        <v>283.7113863125622</v>
       </c>
       <c r="D4">
-        <v>291.6745020390213</v>
+        <v>292.4173863125623</v>
       </c>
       <c r="E4">
-        <v>5.804</v>
+        <v>8.706</v>
       </c>
       <c r="F4">
-        <v>5.804</v>
+        <v>8.706</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1615,28 +1615,28 @@
         <v>62.2</v>
       </c>
       <c r="M4">
-        <v>0.2919412</v>
+        <v>0.4379118</v>
       </c>
       <c r="N4">
-        <v>61.90805880000001</v>
+        <v>61.7620882</v>
       </c>
       <c r="O4">
-        <v>18.57241764</v>
+        <v>18.52862646</v>
       </c>
       <c r="P4">
-        <v>43.33564116000001</v>
+        <v>43.23346174</v>
       </c>
       <c r="Q4">
-        <v>48.83564116000001</v>
+        <v>48.73346174</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1268675047742327</v>
+        <v>0.1274560593319082</v>
       </c>
       <c r="T4">
-        <v>0.5652385201030521</v>
+        <v>0.5693421829468379</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>213.0566018088574</v>
+        <v>142.0377345392383</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.124688677551951</v>
+        <v>0.1243430004251539</v>
       </c>
       <c r="C5">
-        <v>283.7113863125622</v>
+        <v>281.5560644469982</v>
       </c>
       <c r="D5">
-        <v>292.4173863125623</v>
+        <v>293.1640644469982</v>
       </c>
       <c r="E5">
-        <v>8.706</v>
+        <v>11.608</v>
       </c>
       <c r="F5">
-        <v>8.706</v>
+        <v>11.608</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1697,28 +1697,28 @@
         <v>62.2</v>
       </c>
       <c r="M5">
-        <v>0.4379118</v>
+        <v>0.5838824</v>
       </c>
       <c r="N5">
-        <v>61.7620882</v>
+        <v>61.6161176</v>
       </c>
       <c r="O5">
-        <v>18.52862646</v>
+        <v>18.48483528</v>
       </c>
       <c r="P5">
-        <v>43.23346174</v>
+        <v>43.13128232</v>
       </c>
       <c r="Q5">
-        <v>48.73346174</v>
+        <v>48.63128232</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1274560593319082</v>
+        <v>0.1280568754428687</v>
       </c>
       <c r="T5">
-        <v>0.5693421829468379</v>
+        <v>0.5735313387665358</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>142.0377345392383</v>
+        <v>106.5283009044287</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1243430004251539</v>
+        <v>0.1239973232983569</v>
       </c>
       <c r="C6">
-        <v>281.5560644469982</v>
+        <v>279.4045655792245</v>
       </c>
       <c r="D6">
-        <v>293.1640644469982</v>
+        <v>293.9145655792245</v>
       </c>
       <c r="E6">
-        <v>11.608</v>
+        <v>14.51</v>
       </c>
       <c r="F6">
-        <v>11.608</v>
+        <v>14.51</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1779,28 +1779,28 @@
         <v>62.2</v>
       </c>
       <c r="M6">
-        <v>0.5838824</v>
+        <v>0.729853</v>
       </c>
       <c r="N6">
-        <v>61.6161176</v>
+        <v>61.470147</v>
       </c>
       <c r="O6">
-        <v>18.48483528</v>
+        <v>18.4410441</v>
       </c>
       <c r="P6">
-        <v>43.13128232</v>
+        <v>43.02910290000001</v>
       </c>
       <c r="Q6">
-        <v>48.63128232</v>
+        <v>48.52910290000001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1280568754428687</v>
+        <v>0.1286703403140599</v>
       </c>
       <c r="T6">
-        <v>0.5735313387665358</v>
+        <v>0.5778086873403327</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>106.5283009044287</v>
+        <v>85.22264072354297</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1239973232983569</v>
+        <v>0.1236516461715599</v>
       </c>
       <c r="C7">
-        <v>279.4045655792245</v>
+        <v>277.2569191452646</v>
       </c>
       <c r="D7">
-        <v>293.9145655792245</v>
+        <v>294.6689191452646</v>
       </c>
       <c r="E7">
-        <v>14.51</v>
+        <v>17.412</v>
       </c>
       <c r="F7">
-        <v>14.51</v>
+        <v>17.412</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1861,28 +1861,28 @@
         <v>62.2</v>
       </c>
       <c r="M7">
-        <v>0.729853</v>
+        <v>0.8758235999999999</v>
       </c>
       <c r="N7">
-        <v>61.470147</v>
+        <v>61.32417640000001</v>
       </c>
       <c r="O7">
-        <v>18.4410441</v>
+        <v>18.39725292</v>
       </c>
       <c r="P7">
-        <v>43.02910290000001</v>
+        <v>42.92692348000001</v>
       </c>
       <c r="Q7">
-        <v>48.52910290000001</v>
+        <v>48.42692348000001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1286703403140599</v>
+        <v>0.1292968576293191</v>
       </c>
       <c r="T7">
-        <v>0.5778086873403327</v>
+        <v>0.5821770433305934</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>85.22264072354297</v>
+        <v>71.01886726961915</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1236516461715599</v>
+        <v>0.1233059690447629</v>
       </c>
       <c r="C8">
-        <v>277.2569191452646</v>
+        <v>275.1131548841186</v>
       </c>
       <c r="D8">
-        <v>294.6689191452646</v>
+        <v>295.4271548841186</v>
       </c>
       <c r="E8">
-        <v>17.412</v>
+        <v>20.314</v>
       </c>
       <c r="F8">
-        <v>17.412</v>
+        <v>20.314</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1943,28 +1943,28 @@
         <v>62.2</v>
       </c>
       <c r="M8">
-        <v>0.8758235999999999</v>
+        <v>1.0217942</v>
       </c>
       <c r="N8">
-        <v>61.32417640000001</v>
+        <v>61.1782058</v>
       </c>
       <c r="O8">
-        <v>18.39725292</v>
+        <v>18.35346174</v>
       </c>
       <c r="P8">
-        <v>42.92692348000001</v>
+        <v>42.82474406</v>
       </c>
       <c r="Q8">
-        <v>48.42692348000001</v>
+        <v>48.32474406</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1292968576293191</v>
+        <v>0.1299368484352289</v>
       </c>
       <c r="T8">
-        <v>0.5821770433305934</v>
+        <v>0.5866393424604296</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>71.01886726961915</v>
+        <v>60.8733148025307</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1233059690447629</v>
+        <v>0.1229602919179659</v>
       </c>
       <c r="C9">
-        <v>275.1131548841186</v>
+        <v>272.9733028416713</v>
       </c>
       <c r="D9">
-        <v>295.4271548841186</v>
+        <v>296.1893028416713</v>
       </c>
       <c r="E9">
-        <v>20.314</v>
+        <v>23.216</v>
       </c>
       <c r="F9">
-        <v>20.314</v>
+        <v>23.216</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2025,28 +2025,28 @@
         <v>62.2</v>
       </c>
       <c r="M9">
-        <v>1.0217942</v>
+        <v>1.1677648</v>
       </c>
       <c r="N9">
-        <v>61.1782058</v>
+        <v>61.0322352</v>
       </c>
       <c r="O9">
-        <v>18.35346174</v>
+        <v>18.30967056</v>
       </c>
       <c r="P9">
-        <v>42.82474406</v>
+        <v>42.72256464</v>
       </c>
       <c r="Q9">
-        <v>48.32474406</v>
+        <v>48.22256464</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1299368484352289</v>
+        <v>0.1305907520847455</v>
       </c>
       <c r="T9">
-        <v>0.5866393424604296</v>
+        <v>0.5911986480930883</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>60.87331480253069</v>
+        <v>53.26415045221435</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1229602919179659</v>
+        <v>0.1226146147911688</v>
       </c>
       <c r="C10">
-        <v>272.9733028416713</v>
+        <v>270.8373933746609</v>
       </c>
       <c r="D10">
-        <v>296.1893028416713</v>
+        <v>296.9553933746609</v>
       </c>
       <c r="E10">
-        <v>23.216</v>
+        <v>26.118</v>
       </c>
       <c r="F10">
-        <v>23.216</v>
+        <v>26.118</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2107,28 +2107,28 @@
         <v>62.2</v>
       </c>
       <c r="M10">
-        <v>1.1677648</v>
+        <v>1.3137354</v>
       </c>
       <c r="N10">
-        <v>61.0322352</v>
+        <v>60.8862646</v>
       </c>
       <c r="O10">
-        <v>18.30967056</v>
+        <v>18.26587938</v>
       </c>
       <c r="P10">
-        <v>42.72256464</v>
+        <v>42.62038522</v>
       </c>
       <c r="Q10">
-        <v>48.22256464</v>
+        <v>48.12038522</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1305907520847455</v>
+        <v>0.1312590272430427</v>
       </c>
       <c r="T10">
-        <v>0.5911986480930883</v>
+        <v>0.595858158245146</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>53.26415045221435</v>
+        <v>47.34591151307943</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1226146147911688</v>
+        <v>0.1222689376643718</v>
       </c>
       <c r="C11">
-        <v>270.8373933746609</v>
+        <v>268.7054571547094</v>
       </c>
       <c r="D11">
-        <v>296.9553933746609</v>
+        <v>297.7254571547094</v>
       </c>
       <c r="E11">
-        <v>26.118</v>
+        <v>29.02</v>
       </c>
       <c r="F11">
-        <v>26.118</v>
+        <v>29.02</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2189,28 +2189,28 @@
         <v>62.2</v>
       </c>
       <c r="M11">
-        <v>1.3137354</v>
+        <v>1.459706</v>
       </c>
       <c r="N11">
-        <v>60.8862646</v>
+        <v>60.74029400000001</v>
       </c>
       <c r="O11">
-        <v>18.26587938</v>
+        <v>18.2220882</v>
       </c>
       <c r="P11">
-        <v>42.62038522</v>
+        <v>42.5182058</v>
       </c>
       <c r="Q11">
-        <v>48.12038522</v>
+        <v>48.0182058</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1312590272430427</v>
+        <v>0.1319421529604131</v>
       </c>
       <c r="T11">
-        <v>0.595858158245146</v>
+        <v>0.6006212130672495</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>47.34591151307943</v>
+        <v>42.61132036177149</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1222689376643718</v>
+        <v>0.1219232605375748</v>
       </c>
       <c r="C12">
-        <v>268.7054571547094</v>
+        <v>266.5775251724165</v>
       </c>
       <c r="D12">
-        <v>297.7254571547094</v>
+        <v>298.4995251724166</v>
       </c>
       <c r="E12">
-        <v>29.02</v>
+        <v>31.922</v>
       </c>
       <c r="F12">
-        <v>29.02</v>
+        <v>31.922</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2271,28 +2271,28 @@
         <v>62.2</v>
       </c>
       <c r="M12">
-        <v>1.459706</v>
+        <v>1.6056766</v>
       </c>
       <c r="N12">
-        <v>60.74029400000001</v>
+        <v>60.5943234</v>
       </c>
       <c r="O12">
-        <v>18.2220882</v>
+        <v>18.17829702</v>
       </c>
       <c r="P12">
-        <v>42.5182058</v>
+        <v>42.41602638000001</v>
       </c>
       <c r="Q12">
-        <v>48.0182058</v>
+        <v>47.91602638000001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1319421529604131</v>
+        <v>0.1326406298174997</v>
       </c>
       <c r="T12">
-        <v>0.6006212130672495</v>
+        <v>0.6054913028291755</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>42.61132036177148</v>
+        <v>38.7375639652468</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1219232605375748</v>
+        <v>0.1215775834107777</v>
       </c>
       <c r="C13">
-        <v>266.5775251724165</v>
+        <v>264.4536287415166</v>
       </c>
       <c r="D13">
-        <v>298.4995251724166</v>
+        <v>299.2776287415167</v>
       </c>
       <c r="E13">
-        <v>31.922</v>
+        <v>34.824</v>
       </c>
       <c r="F13">
-        <v>31.922</v>
+        <v>34.824</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2353,28 +2353,28 @@
         <v>62.2</v>
       </c>
       <c r="M13">
-        <v>1.6056766</v>
+        <v>1.7516472</v>
       </c>
       <c r="N13">
-        <v>60.5943234</v>
+        <v>60.4483528</v>
       </c>
       <c r="O13">
-        <v>18.17829702</v>
+        <v>18.13450584</v>
       </c>
       <c r="P13">
-        <v>42.41602638000001</v>
+        <v>42.31384696000001</v>
       </c>
       <c r="Q13">
-        <v>47.91602638000001</v>
+        <v>47.81384696000001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1326406298174997</v>
+        <v>0.1333549811486111</v>
       </c>
       <c r="T13">
-        <v>0.6054913028291755</v>
+        <v>0.6104720764493271</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>38.7375639652468</v>
+        <v>35.50943363480957</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1215775834107777</v>
+        <v>0.1212319062839807</v>
       </c>
       <c r="C14">
-        <v>264.4536287415166</v>
+        <v>262.3337995031015</v>
       </c>
       <c r="D14">
-        <v>299.2776287415167</v>
+        <v>300.0597995031015</v>
       </c>
       <c r="E14">
-        <v>34.824</v>
+        <v>37.726</v>
       </c>
       <c r="F14">
-        <v>34.824</v>
+        <v>37.726</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2435,28 +2435,28 @@
         <v>62.2</v>
       </c>
       <c r="M14">
-        <v>1.7516472</v>
+        <v>1.8976178</v>
       </c>
       <c r="N14">
-        <v>60.4483528</v>
+        <v>60.3023822</v>
       </c>
       <c r="O14">
-        <v>18.13450584</v>
+        <v>18.09071466</v>
       </c>
       <c r="P14">
-        <v>42.31384696000001</v>
+        <v>42.21166754000001</v>
       </c>
       <c r="Q14">
-        <v>47.81384696000001</v>
+        <v>47.71166754000001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1333549811486111</v>
+        <v>0.1340857543494031</v>
       </c>
       <c r="T14">
-        <v>0.6104720764493271</v>
+        <v>0.6155673506124707</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>35.50943363480957</v>
+        <v>32.77793873982422</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1212319062839807</v>
+        <v>0.1208862291571837</v>
       </c>
       <c r="C15">
-        <v>262.3337995031015</v>
+        <v>260.2180694299093</v>
       </c>
       <c r="D15">
-        <v>300.0597995031015</v>
+        <v>300.8460694299093</v>
       </c>
       <c r="E15">
-        <v>37.726</v>
+        <v>40.628</v>
       </c>
       <c r="F15">
-        <v>37.726</v>
+        <v>40.628</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2517,28 +2517,28 @@
         <v>62.2</v>
       </c>
       <c r="M15">
-        <v>1.8976178</v>
+        <v>2.0435884</v>
       </c>
       <c r="N15">
-        <v>60.3023822</v>
+        <v>60.15641160000001</v>
       </c>
       <c r="O15">
-        <v>18.09071466</v>
+        <v>18.04692348</v>
       </c>
       <c r="P15">
-        <v>42.21166754000001</v>
+        <v>42.10948812000001</v>
       </c>
       <c r="Q15">
-        <v>47.71166754000001</v>
+        <v>47.60948812000001</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1340857543494031</v>
+        <v>0.134833522275795</v>
       </c>
       <c r="T15">
-        <v>0.6155673506124707</v>
+        <v>0.6207811195235944</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>32.77793873982422</v>
+        <v>30.43665740126535</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1208862291571837</v>
+        <v>0.1205405520303867</v>
       </c>
       <c r="C16">
-        <v>260.2180694299093</v>
+        <v>258.1064708306812</v>
       </c>
       <c r="D16">
-        <v>300.8460694299093</v>
+        <v>301.6364708306812</v>
       </c>
       <c r="E16">
-        <v>40.628</v>
+        <v>43.53000000000001</v>
       </c>
       <c r="F16">
-        <v>40.628</v>
+        <v>43.53000000000001</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2599,28 +2599,28 @@
         <v>62.2</v>
       </c>
       <c r="M16">
-        <v>2.0435884</v>
+        <v>2.189559</v>
       </c>
       <c r="N16">
-        <v>60.15641160000001</v>
+        <v>60.010441</v>
       </c>
       <c r="O16">
-        <v>18.04692348</v>
+        <v>18.0031323</v>
       </c>
       <c r="P16">
-        <v>42.10948812000001</v>
+        <v>42.0073087</v>
       </c>
       <c r="Q16">
-        <v>47.60948812000001</v>
+        <v>47.5073087</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.134833522275795</v>
+        <v>0.1355988847416314</v>
       </c>
       <c r="T16">
-        <v>0.6207811195235944</v>
+        <v>0.6261175653502741</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>30.43665740126535</v>
+        <v>28.40754690784765</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1205405520303867</v>
+        <v>0.1201948749035896</v>
       </c>
       <c r="C17">
-        <v>258.1064708306812</v>
+        <v>255.999036354587</v>
       </c>
       <c r="D17">
-        <v>301.6364708306812</v>
+        <v>302.431036354587</v>
       </c>
       <c r="E17">
-        <v>43.52999999999999</v>
+        <v>46.432</v>
       </c>
       <c r="F17">
-        <v>43.52999999999999</v>
+        <v>46.432</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2681,28 +2681,28 @@
         <v>62.2</v>
       </c>
       <c r="M17">
-        <v>2.189559</v>
+        <v>2.3355296</v>
       </c>
       <c r="N17">
-        <v>60.010441</v>
+        <v>59.8644704</v>
       </c>
       <c r="O17">
-        <v>18.0031323</v>
+        <v>17.95934112</v>
       </c>
       <c r="P17">
-        <v>42.0073087</v>
+        <v>41.90512928</v>
       </c>
       <c r="Q17">
-        <v>47.5073087</v>
+        <v>47.40512928</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1355988847416314</v>
+        <v>0.136382470123321</v>
       </c>
       <c r="T17">
-        <v>0.6261175653502741</v>
+        <v>0.6315810694109221</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>28.40754690784766</v>
+        <v>26.63207522610718</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1201948749035896</v>
+        <v>0.1198491977767926</v>
       </c>
       <c r="C18">
-        <v>255.999036354587</v>
+        <v>253.8957989957204</v>
       </c>
       <c r="D18">
-        <v>302.431036354587</v>
+        <v>303.2297989957204</v>
       </c>
       <c r="E18">
-        <v>46.432</v>
+        <v>49.334</v>
       </c>
       <c r="F18">
-        <v>46.432</v>
+        <v>49.334</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2763,28 +2763,28 @@
         <v>62.2</v>
       </c>
       <c r="M18">
-        <v>2.3355296</v>
+        <v>2.4815002</v>
       </c>
       <c r="N18">
-        <v>59.8644704</v>
+        <v>59.7184998</v>
       </c>
       <c r="O18">
-        <v>17.95934112</v>
+        <v>17.91554994</v>
       </c>
       <c r="P18">
-        <v>41.90512928</v>
+        <v>41.80294986</v>
       </c>
       <c r="Q18">
-        <v>47.40512928</v>
+        <v>47.30294986</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.136382470123321</v>
+        <v>0.1371849370804731</v>
       </c>
       <c r="T18">
-        <v>0.6315810694109221</v>
+        <v>0.6371762241718268</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>26.63207522610718</v>
+        <v>25.06548256574793</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1198491977767926</v>
+        <v>0.1195035206499956</v>
       </c>
       <c r="C19">
-        <v>253.8957989957204</v>
+        <v>251.7967920976665</v>
       </c>
       <c r="D19">
-        <v>303.2297989957204</v>
+        <v>304.0327920976665</v>
       </c>
       <c r="E19">
-        <v>49.334</v>
+        <v>52.236</v>
       </c>
       <c r="F19">
-        <v>49.334</v>
+        <v>52.236</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2845,28 +2845,28 @@
         <v>62.2</v>
       </c>
       <c r="M19">
-        <v>2.4815002</v>
+        <v>2.6274708</v>
       </c>
       <c r="N19">
-        <v>59.7184998</v>
+        <v>59.57252920000001</v>
       </c>
       <c r="O19">
-        <v>17.91554994</v>
+        <v>17.87175876</v>
       </c>
       <c r="P19">
-        <v>41.80294986</v>
+        <v>41.70077044</v>
       </c>
       <c r="Q19">
-        <v>47.30294986</v>
+        <v>47.20077044</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1371849370804731</v>
+        <v>0.1380069764024336</v>
       </c>
       <c r="T19">
-        <v>0.6371762241718268</v>
+        <v>0.6429078461220218</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>25.06548256574793</v>
+        <v>23.67295575653971</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1195035206499956</v>
+        <v>0.1191578435231986</v>
       </c>
       <c r="C20">
-        <v>251.7967920976665</v>
+        <v>249.7020493581407</v>
       </c>
       <c r="D20">
-        <v>304.0327920976665</v>
+        <v>304.8400493581407</v>
       </c>
       <c r="E20">
-        <v>52.236</v>
+        <v>55.138</v>
       </c>
       <c r="F20">
-        <v>52.236</v>
+        <v>55.138</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2927,28 +2927,28 @@
         <v>62.2</v>
       </c>
       <c r="M20">
-        <v>2.6274708</v>
+        <v>2.7734414</v>
       </c>
       <c r="N20">
-        <v>59.57252920000001</v>
+        <v>59.4265586</v>
       </c>
       <c r="O20">
-        <v>17.87175876</v>
+        <v>17.82796758</v>
       </c>
       <c r="P20">
-        <v>41.70077044</v>
+        <v>41.59859102</v>
       </c>
       <c r="Q20">
-        <v>47.20077044</v>
+        <v>47.09859102</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1380069764024336</v>
+        <v>0.1388493129916032</v>
       </c>
       <c r="T20">
-        <v>0.6429078461220218</v>
+        <v>0.6487809896018514</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>23.67295575653971</v>
+        <v>22.42701071672183</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1191578435231986</v>
+        <v>0.1188121663964015</v>
       </c>
       <c r="C21">
-        <v>249.7020493581407</v>
+        <v>247.6116048337039</v>
       </c>
       <c r="D21">
-        <v>304.8400493581407</v>
+        <v>305.6516048337039</v>
       </c>
       <c r="E21">
-        <v>55.138</v>
+        <v>58.04</v>
       </c>
       <c r="F21">
-        <v>55.138</v>
+        <v>58.04</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -3009,28 +3009,28 @@
         <v>62.2</v>
       </c>
       <c r="M21">
-        <v>2.7734414</v>
+        <v>2.919412</v>
       </c>
       <c r="N21">
-        <v>59.4265586</v>
+        <v>59.280588</v>
       </c>
       <c r="O21">
-        <v>17.82796758</v>
+        <v>17.7841764</v>
       </c>
       <c r="P21">
-        <v>41.59859102</v>
+        <v>41.4964116</v>
       </c>
       <c r="Q21">
-        <v>47.09859102</v>
+        <v>46.9964116</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1388493129916032</v>
+        <v>0.1397127079955019</v>
       </c>
       <c r="T21">
-        <v>0.6487809896018514</v>
+        <v>0.6548009616686766</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>22.42701071672183</v>
+        <v>21.30566018088574</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1188121663964015</v>
+        <v>0.1184664892696045</v>
       </c>
       <c r="C22">
-        <v>247.6116048337039</v>
+        <v>245.5254929445508</v>
       </c>
       <c r="D22">
-        <v>305.6516048337039</v>
+        <v>306.4674929445508</v>
       </c>
       <c r="E22">
-        <v>58.04</v>
+        <v>60.942</v>
       </c>
       <c r="F22">
-        <v>58.04</v>
+        <v>60.942</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3091,28 +3091,28 @@
         <v>62.2</v>
       </c>
       <c r="M22">
-        <v>2.919412</v>
+        <v>3.0653826</v>
       </c>
       <c r="N22">
-        <v>59.280588</v>
+        <v>59.1346174</v>
       </c>
       <c r="O22">
-        <v>17.7841764</v>
+        <v>17.74038522</v>
       </c>
       <c r="P22">
-        <v>41.4964116</v>
+        <v>41.39423218</v>
       </c>
       <c r="Q22">
-        <v>46.9964116</v>
+        <v>46.89423218</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1397127079955019</v>
+        <v>0.1405979611007652</v>
       </c>
       <c r="T22">
-        <v>0.6548009616686766</v>
+        <v>0.6609733380916241</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>21.30566018088574</v>
+        <v>20.2911049341769</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1184664892696045</v>
+        <v>0.1181208121428075</v>
       </c>
       <c r="C23">
-        <v>245.5254929445508</v>
+        <v>243.4437484793766</v>
       </c>
       <c r="D23">
-        <v>306.4674929445508</v>
+        <v>307.2877484793765</v>
       </c>
       <c r="E23">
-        <v>60.94199999999999</v>
+        <v>63.844</v>
       </c>
       <c r="F23">
-        <v>60.94199999999999</v>
+        <v>63.844</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3173,28 +3173,28 @@
         <v>62.2</v>
       </c>
       <c r="M23">
-        <v>3.0653826</v>
+        <v>3.2113532</v>
       </c>
       <c r="N23">
-        <v>59.1346174</v>
+        <v>58.98864680000001</v>
       </c>
       <c r="O23">
-        <v>17.74038522</v>
+        <v>17.69659404</v>
       </c>
       <c r="P23">
-        <v>41.39423218</v>
+        <v>41.29205276</v>
       </c>
       <c r="Q23">
-        <v>46.89423218</v>
+        <v>46.79205276</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1405979611007652</v>
+        <v>0.1415059130035994</v>
       </c>
       <c r="T23">
-        <v>0.660973338091624</v>
+        <v>0.6673039805766983</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>20.2911049341769</v>
+        <v>19.3687819826234</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1181208121428075</v>
+        <v>0.1177751350160105</v>
       </c>
       <c r="C24">
-        <v>243.4437484793766</v>
+        <v>241.3664066003216</v>
       </c>
       <c r="D24">
-        <v>307.2877484793765</v>
+        <v>308.1124066003216</v>
       </c>
       <c r="E24">
-        <v>63.844</v>
+        <v>66.746</v>
       </c>
       <c r="F24">
-        <v>63.844</v>
+        <v>66.746</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3255,28 +3255,28 @@
         <v>62.2</v>
       </c>
       <c r="M24">
-        <v>3.2113532</v>
+        <v>3.3573238</v>
       </c>
       <c r="N24">
-        <v>58.98864680000001</v>
+        <v>58.8426762</v>
       </c>
       <c r="O24">
-        <v>17.69659404</v>
+        <v>17.65280286</v>
       </c>
       <c r="P24">
-        <v>41.29205276</v>
+        <v>41.18987334000001</v>
       </c>
       <c r="Q24">
-        <v>46.79205276</v>
+        <v>46.68987334000001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1415059130035994</v>
+        <v>0.1424374480727409</v>
       </c>
       <c r="T24">
-        <v>0.6673039805766983</v>
+        <v>0.6737990553341121</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>19.3687819826234</v>
+        <v>18.52666102685717</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1177751350160105</v>
+        <v>0.1174294578892134</v>
       </c>
       <c r="C25">
-        <v>241.3664066003216</v>
+        <v>239.2935028479961</v>
       </c>
       <c r="D25">
-        <v>308.1124066003216</v>
+        <v>308.941502847996</v>
       </c>
       <c r="E25">
-        <v>66.746</v>
+        <v>69.648</v>
       </c>
       <c r="F25">
-        <v>66.746</v>
+        <v>69.648</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3337,28 +3337,28 @@
         <v>62.2</v>
       </c>
       <c r="M25">
-        <v>3.3573238</v>
+        <v>3.5032944</v>
       </c>
       <c r="N25">
-        <v>58.8426762</v>
+        <v>58.6967056</v>
       </c>
       <c r="O25">
-        <v>17.65280286</v>
+        <v>17.60901168</v>
       </c>
       <c r="P25">
-        <v>41.18987334000001</v>
+        <v>41.08769392000001</v>
       </c>
       <c r="Q25">
-        <v>46.68987334000001</v>
+        <v>46.58769392000001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1424374480727409</v>
+        <v>0.1433934972226493</v>
       </c>
       <c r="T25">
-        <v>0.6737990553341121</v>
+        <v>0.6804650531114579</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>18.52666102685717</v>
+        <v>17.75471681740478</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1174294578892134</v>
+        <v>0.1170837807624164</v>
       </c>
       <c r="C26">
-        <v>239.2935028479961</v>
+        <v>237.2250731465853</v>
       </c>
       <c r="D26">
-        <v>308.941502847996</v>
+        <v>309.7750731465853</v>
       </c>
       <c r="E26">
-        <v>69.648</v>
+        <v>72.55</v>
       </c>
       <c r="F26">
-        <v>69.648</v>
+        <v>72.55</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3419,28 +3419,28 @@
         <v>62.2</v>
       </c>
       <c r="M26">
-        <v>3.5032944</v>
+        <v>3.649265</v>
       </c>
       <c r="N26">
-        <v>58.6967056</v>
+        <v>58.550735</v>
       </c>
       <c r="O26">
-        <v>17.60901168</v>
+        <v>17.5652205</v>
       </c>
       <c r="P26">
-        <v>41.08769392000001</v>
+        <v>40.98551450000001</v>
       </c>
       <c r="Q26">
-        <v>46.58769392000001</v>
+        <v>46.48551450000001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1433934972226493</v>
+        <v>0.1443750410165552</v>
       </c>
       <c r="T26">
-        <v>0.6804650531114579</v>
+        <v>0.687308810829533</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>17.75471681740478</v>
+        <v>17.04452814470859</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1170837807624164</v>
+        <v>0.1167381036356194</v>
       </c>
       <c r="C27">
-        <v>237.2250731465853</v>
+        <v>235.1611538090394</v>
       </c>
       <c r="D27">
-        <v>309.7750731465853</v>
+        <v>310.6131538090394</v>
       </c>
       <c r="E27">
-        <v>72.55</v>
+        <v>75.452</v>
       </c>
       <c r="F27">
-        <v>72.55</v>
+        <v>75.452</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -3501,28 +3501,28 @@
         <v>62.2</v>
       </c>
       <c r="M27">
-        <v>3.649265</v>
+        <v>3.7952356</v>
       </c>
       <c r="N27">
-        <v>58.550735</v>
+        <v>58.4047644</v>
       </c>
       <c r="O27">
-        <v>17.5652205</v>
+        <v>17.52142932</v>
       </c>
       <c r="P27">
-        <v>40.98551450000001</v>
+        <v>40.88333508000001</v>
       </c>
       <c r="Q27">
-        <v>46.48551450000001</v>
+        <v>46.38333508000001</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1443750410165552</v>
+        <v>0.1453831130211073</v>
       </c>
       <c r="T27">
-        <v>0.687308810829533</v>
+        <v>0.6943375349724207</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>17.04452814470859</v>
+        <v>16.38896936991211</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1167381036356194</v>
+        <v>0.1163924265088224</v>
       </c>
       <c r="C28">
-        <v>235.1611538090394</v>
+        <v>233.1017815423451</v>
       </c>
       <c r="D28">
-        <v>310.6131538090394</v>
+        <v>311.4557815423451</v>
       </c>
       <c r="E28">
-        <v>75.452</v>
+        <v>78.354</v>
       </c>
       <c r="F28">
-        <v>75.452</v>
+        <v>78.354</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3583,28 +3583,28 @@
         <v>62.2</v>
       </c>
       <c r="M28">
-        <v>3.7952356</v>
+        <v>3.9412062</v>
       </c>
       <c r="N28">
-        <v>58.4047644</v>
+        <v>58.25879380000001</v>
       </c>
       <c r="O28">
-        <v>17.52142932</v>
+        <v>17.47763814</v>
       </c>
       <c r="P28">
-        <v>40.88333508000001</v>
+        <v>40.78115566000001</v>
       </c>
       <c r="Q28">
-        <v>46.38333508000001</v>
+        <v>46.28115566000001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1453831130211073</v>
+        <v>0.146418803436743</v>
       </c>
       <c r="T28">
-        <v>0.6943375349724207</v>
+        <v>0.7015588269000453</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>16.38896936991211</v>
+        <v>15.78197050435981</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1163924265088224</v>
+        <v>0.1160467493820253</v>
       </c>
       <c r="C29">
-        <v>233.1017815423451</v>
+        <v>231.0469934528864</v>
       </c>
       <c r="D29">
-        <v>311.4557815423451</v>
+        <v>312.3029934528864</v>
       </c>
       <c r="E29">
-        <v>78.354</v>
+        <v>81.256</v>
       </c>
       <c r="F29">
-        <v>78.354</v>
+        <v>81.256</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -3665,28 +3665,28 @@
         <v>62.2</v>
       </c>
       <c r="M29">
-        <v>3.9412062</v>
+        <v>4.0871768</v>
       </c>
       <c r="N29">
-        <v>58.25879380000001</v>
+        <v>58.1128232</v>
       </c>
       <c r="O29">
-        <v>17.47763814</v>
+        <v>17.43384696</v>
       </c>
       <c r="P29">
-        <v>40.78115566000001</v>
+        <v>40.67897624</v>
       </c>
       <c r="Q29">
-        <v>46.28115566000001</v>
+        <v>46.17897624</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.146418803436743</v>
+        <v>0.1474832630305907</v>
       </c>
       <c r="T29">
-        <v>0.7015588269000453</v>
+        <v>0.7089807102701037</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>15.78197050435981</v>
+        <v>15.21832870063267</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1160467493820253</v>
+        <v>0.1157010722552283</v>
       </c>
       <c r="C30">
-        <v>231.0469934528864</v>
+        <v>228.9968270518904</v>
       </c>
       <c r="D30">
-        <v>312.3029934528864</v>
+        <v>313.1548270518904</v>
       </c>
       <c r="E30">
-        <v>81.256</v>
+        <v>84.158</v>
       </c>
       <c r="F30">
-        <v>81.256</v>
+        <v>84.158</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -3747,28 +3747,28 @@
         <v>62.2</v>
       </c>
       <c r="M30">
-        <v>4.0871768</v>
+        <v>4.2331474</v>
       </c>
       <c r="N30">
-        <v>58.1128232</v>
+        <v>57.9668526</v>
       </c>
       <c r="O30">
-        <v>17.43384696</v>
+        <v>17.39005578</v>
       </c>
       <c r="P30">
-        <v>40.67897624</v>
+        <v>40.57679682</v>
       </c>
       <c r="Q30">
-        <v>46.17897624</v>
+        <v>46.07679682</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1474832630305907</v>
+        <v>0.14857770740173</v>
       </c>
       <c r="T30">
-        <v>0.7089807102701037</v>
+        <v>0.7166116607773471</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>15.21832870063267</v>
+        <v>14.69355874543844</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1157010722552283</v>
+        <v>0.1153553951284313</v>
       </c>
       <c r="C31">
-        <v>228.9968270518904</v>
+        <v>226.9513202609646</v>
       </c>
       <c r="D31">
-        <v>313.1548270518904</v>
+        <v>314.0113202609646</v>
       </c>
       <c r="E31">
-        <v>84.15799999999999</v>
+        <v>87.05999999999999</v>
       </c>
       <c r="F31">
-        <v>84.15799999999999</v>
+        <v>87.05999999999999</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -3829,28 +3829,28 @@
         <v>62.2</v>
       </c>
       <c r="M31">
-        <v>4.233147399999999</v>
+        <v>4.379117999999999</v>
       </c>
       <c r="N31">
-        <v>57.9668526</v>
+        <v>57.820882</v>
       </c>
       <c r="O31">
-        <v>17.39005578</v>
+        <v>17.3462646</v>
       </c>
       <c r="P31">
-        <v>40.57679682</v>
+        <v>40.4746174</v>
       </c>
       <c r="Q31">
-        <v>46.07679682</v>
+        <v>45.9746174</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.14857770740173</v>
+        <v>0.1497034216120447</v>
       </c>
       <c r="T31">
-        <v>0.7166116607773471</v>
+        <v>0.7244606384419401</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>14.69355874543844</v>
+        <v>14.20377345392383</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1153553951284313</v>
+        <v>0.1150097180016343</v>
       </c>
       <c r="C32">
-        <v>226.9513202609646</v>
+        <v>224.9105114177233</v>
       </c>
       <c r="D32">
-        <v>314.0113202609646</v>
+        <v>314.8725114177233</v>
       </c>
       <c r="E32">
-        <v>87.05999999999999</v>
+        <v>89.96199999999999</v>
       </c>
       <c r="F32">
-        <v>87.05999999999999</v>
+        <v>89.96199999999999</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -3911,28 +3911,28 @@
         <v>62.2</v>
       </c>
       <c r="M32">
-        <v>4.379117999999999</v>
+        <v>4.525088599999999</v>
       </c>
       <c r="N32">
-        <v>57.820882</v>
+        <v>57.67491140000001</v>
       </c>
       <c r="O32">
-        <v>17.3462646</v>
+        <v>17.30247342</v>
       </c>
       <c r="P32">
-        <v>40.4746174</v>
+        <v>40.37243798</v>
       </c>
       <c r="Q32">
-        <v>45.9746174</v>
+        <v>45.87243798</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1497034216120447</v>
+        <v>0.1508617652197598</v>
       </c>
       <c r="T32">
-        <v>0.7244606384419401</v>
+        <v>0.7325371227055069</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>14.20377345392383</v>
+        <v>13.74558721347467</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1150097180016343</v>
+        <v>0.1146640408748372</v>
       </c>
       <c r="C33">
-        <v>224.9105114177233</v>
+        <v>222.8744392815088</v>
       </c>
       <c r="D33">
-        <v>314.8725114177233</v>
+        <v>315.7384392815088</v>
       </c>
       <c r="E33">
-        <v>89.96199999999999</v>
+        <v>92.864</v>
       </c>
       <c r="F33">
-        <v>89.96199999999999</v>
+        <v>92.864</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -3993,28 +3993,28 @@
         <v>62.2</v>
       </c>
       <c r="M33">
-        <v>4.525088599999999</v>
+        <v>4.6710592</v>
       </c>
       <c r="N33">
-        <v>57.67491140000001</v>
+        <v>57.5289408</v>
       </c>
       <c r="O33">
-        <v>17.30247342</v>
+        <v>17.25868224</v>
       </c>
       <c r="P33">
-        <v>40.37243798</v>
+        <v>40.27025856</v>
       </c>
       <c r="Q33">
-        <v>45.87243798</v>
+        <v>45.77025856</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1508617652197598</v>
+        <v>0.1520541777571136</v>
       </c>
       <c r="T33">
-        <v>0.7325371227055069</v>
+        <v>0.7408511506238844</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>13.74558721347467</v>
+        <v>13.31603761305359</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1146640408748372</v>
+        <v>0.1143183637480402</v>
       </c>
       <c r="C34">
-        <v>222.8744392815088</v>
+        <v>220.8431430392058</v>
       </c>
       <c r="D34">
-        <v>315.7384392815088</v>
+        <v>316.6091430392058</v>
       </c>
       <c r="E34">
-        <v>92.864</v>
+        <v>95.76600000000001</v>
       </c>
       <c r="F34">
-        <v>92.864</v>
+        <v>95.76600000000001</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -4075,28 +4075,28 @@
         <v>62.2</v>
       </c>
       <c r="M34">
-        <v>4.6710592</v>
+        <v>4.8170298</v>
       </c>
       <c r="N34">
-        <v>57.5289408</v>
+        <v>57.3829702</v>
       </c>
       <c r="O34">
-        <v>17.25868224</v>
+        <v>17.21489106</v>
       </c>
       <c r="P34">
-        <v>40.27025856</v>
+        <v>40.16807914</v>
       </c>
       <c r="Q34">
-        <v>45.77025856</v>
+        <v>45.66807914</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1520541777571136</v>
+        <v>0.1532821846985675</v>
       </c>
       <c r="T34">
-        <v>0.7408511506238844</v>
+        <v>0.7494133584801241</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>13.31603761305359</v>
+        <v>12.91252132174893</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1143183637480402</v>
+        <v>0.1143296866212432</v>
       </c>
       <c r="C35">
-        <v>220.8431430392058</v>
+        <v>217.9125465191995</v>
       </c>
       <c r="D35">
-        <v>316.6091430392058</v>
+        <v>316.5805465191995</v>
       </c>
       <c r="E35">
-        <v>95.76600000000001</v>
+        <v>98.66800000000001</v>
       </c>
       <c r="F35">
-        <v>95.76600000000001</v>
+        <v>98.66800000000001</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -4157,45 +4157,45 @@
         <v>62.2</v>
       </c>
       <c r="M35">
-        <v>4.8170298</v>
+        <v>5.1110024</v>
       </c>
       <c r="N35">
-        <v>57.3829702</v>
+        <v>57.0889976</v>
       </c>
       <c r="O35">
-        <v>17.21489106</v>
+        <v>17.12669928</v>
       </c>
       <c r="P35">
-        <v>40.16807914</v>
+        <v>39.96229832</v>
       </c>
       <c r="Q35">
-        <v>45.66807914</v>
+        <v>45.46229832</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1532821846985675</v>
+        <v>0.1545474039715806</v>
       </c>
       <c r="T35">
-        <v>0.7494133584801241</v>
+        <v>0.7582350271804921</v>
       </c>
       <c r="U35">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V35">
         <v>0.3</v>
       </c>
       <c r="W35">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y35">
-        <v>12.91252132174893</v>
+        <v>12.16982406425792</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1143296866212432</v>
+        <v>0.1139945094944461</v>
       </c>
       <c r="C36">
-        <v>217.9125465191995</v>
+        <v>215.8592469098693</v>
       </c>
       <c r="D36">
-        <v>316.5805465191995</v>
+        <v>317.4292469098693</v>
       </c>
       <c r="E36">
-        <v>98.66800000000001</v>
+        <v>101.57</v>
       </c>
       <c r="F36">
-        <v>98.66800000000001</v>
+        <v>101.57</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -4239,28 +4239,28 @@
         <v>62.2</v>
       </c>
       <c r="M36">
-        <v>5.1110024</v>
+        <v>5.261326</v>
       </c>
       <c r="N36">
-        <v>57.0889976</v>
+        <v>56.93867400000001</v>
       </c>
       <c r="O36">
-        <v>17.12669928</v>
+        <v>17.0816022</v>
       </c>
       <c r="P36">
-        <v>39.96229832</v>
+        <v>39.8570718</v>
       </c>
       <c r="Q36">
-        <v>45.46229832</v>
+        <v>45.3570718</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1545474039715806</v>
+        <v>0.1558515530683787</v>
       </c>
       <c r="T36">
-        <v>0.7582350271804921</v>
+        <v>0.7673281318408715</v>
       </c>
       <c r="U36">
         <v>0.0518</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>12.16982406425792</v>
+        <v>11.82211480527913</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1139945094944461</v>
+        <v>0.1136593323676491</v>
       </c>
       <c r="C37">
-        <v>215.8592469098693</v>
+        <v>213.8105099847405</v>
       </c>
       <c r="D37">
-        <v>317.4292469098693</v>
+        <v>318.2825099847405</v>
       </c>
       <c r="E37">
-        <v>101.57</v>
+        <v>104.472</v>
       </c>
       <c r="F37">
-        <v>101.57</v>
+        <v>104.472</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -4321,28 +4321,28 @@
         <v>62.2</v>
       </c>
       <c r="M37">
-        <v>5.261326</v>
+        <v>5.411649600000001</v>
       </c>
       <c r="N37">
-        <v>56.93867400000001</v>
+        <v>56.7883504</v>
       </c>
       <c r="O37">
-        <v>17.0816022</v>
+        <v>17.03650512</v>
       </c>
       <c r="P37">
-        <v>39.8570718</v>
+        <v>39.75184528</v>
       </c>
       <c r="Q37">
-        <v>45.3570718</v>
+        <v>45.25184528</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1558515530683787</v>
+        <v>0.1571964568244518</v>
       </c>
       <c r="T37">
-        <v>0.7673281318408715</v>
+        <v>0.7767053960218877</v>
       </c>
       <c r="U37">
         <v>0.0518</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>11.82211480527913</v>
+        <v>11.4937227273547</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1136593323676491</v>
+        <v>0.1133241552408521</v>
       </c>
       <c r="C38">
-        <v>213.8105099847405</v>
+        <v>211.766372637041</v>
       </c>
       <c r="D38">
-        <v>318.2825099847405</v>
+        <v>319.140372637041</v>
       </c>
       <c r="E38">
-        <v>104.472</v>
+        <v>107.374</v>
       </c>
       <c r="F38">
-        <v>104.472</v>
+        <v>107.374</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -4403,28 +4403,28 @@
         <v>62.2</v>
       </c>
       <c r="M38">
-        <v>5.4116496</v>
+        <v>5.5619732</v>
       </c>
       <c r="N38">
-        <v>56.78835040000001</v>
+        <v>56.63802680000001</v>
       </c>
       <c r="O38">
-        <v>17.03650512</v>
+        <v>16.99140804</v>
       </c>
       <c r="P38">
-        <v>39.75184528</v>
+        <v>39.64661876000001</v>
       </c>
       <c r="Q38">
-        <v>45.25184528</v>
+        <v>45.14661876000001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1571964568244518</v>
+        <v>0.1585840559378605</v>
       </c>
       <c r="T38">
-        <v>0.7767053960218877</v>
+        <v>0.7863803511292853</v>
       </c>
       <c r="U38">
         <v>0.0518</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>11.49372272735471</v>
+        <v>11.18308157256134</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1133241552408521</v>
+        <v>0.1129889781140551</v>
       </c>
       <c r="C39">
-        <v>211.766372637041</v>
+        <v>209.7268721588247</v>
       </c>
       <c r="D39">
-        <v>319.140372637041</v>
+        <v>320.0028721588247</v>
       </c>
       <c r="E39">
-        <v>107.374</v>
+        <v>110.276</v>
       </c>
       <c r="F39">
-        <v>107.374</v>
+        <v>110.276</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -4485,28 +4485,28 @@
         <v>62.2</v>
       </c>
       <c r="M39">
-        <v>5.5619732</v>
+        <v>5.7122968</v>
       </c>
       <c r="N39">
-        <v>56.63802680000001</v>
+        <v>56.48770320000001</v>
       </c>
       <c r="O39">
-        <v>16.99140804</v>
+        <v>16.94631096</v>
       </c>
       <c r="P39">
-        <v>39.64661876000001</v>
+        <v>39.54139224000001</v>
       </c>
       <c r="Q39">
-        <v>45.14661876000001</v>
+        <v>45.04139224000001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1585840559378605</v>
+        <v>0.160016416312992</v>
       </c>
       <c r="T39">
-        <v>0.7863803511292853</v>
+        <v>0.7963674015627281</v>
       </c>
       <c r="U39">
         <v>0.0518</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>11.18308157256134</v>
+        <v>10.88878995223078</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1129889781140551</v>
+        <v>0.1126538009872581</v>
       </c>
       <c r="C40">
-        <v>209.7268721588247</v>
+        <v>207.6920462463755</v>
       </c>
       <c r="D40">
-        <v>320.0028721588247</v>
+        <v>320.8700462463755</v>
       </c>
       <c r="E40">
-        <v>110.276</v>
+        <v>113.178</v>
       </c>
       <c r="F40">
-        <v>110.276</v>
+        <v>113.178</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -4567,28 +4567,28 @@
         <v>62.2</v>
       </c>
       <c r="M40">
-        <v>5.7122968</v>
+        <v>5.8626204</v>
       </c>
       <c r="N40">
-        <v>56.48770320000001</v>
+        <v>56.33737960000001</v>
       </c>
       <c r="O40">
-        <v>16.94631096</v>
+        <v>16.90121388</v>
       </c>
       <c r="P40">
-        <v>39.54139224000001</v>
+        <v>39.43616572000001</v>
       </c>
       <c r="Q40">
-        <v>45.04139224000001</v>
+        <v>44.93616572000001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.160016416312992</v>
+        <v>0.1614957393233739</v>
       </c>
       <c r="T40">
-        <v>0.7963674015627281</v>
+        <v>0.8066818962726773</v>
       </c>
       <c r="U40">
         <v>0.0518</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>10.88878995223078</v>
+        <v>10.60959020986588</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1126538009872581</v>
+        <v>0.112318623860461</v>
       </c>
       <c r="C41">
-        <v>207.6920462463755</v>
+        <v>205.6619330057001</v>
       </c>
       <c r="D41">
-        <v>320.8700462463755</v>
+        <v>321.7419330057</v>
       </c>
       <c r="E41">
-        <v>113.178</v>
+        <v>116.08</v>
       </c>
       <c r="F41">
-        <v>113.178</v>
+        <v>116.08</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -4649,28 +4649,28 @@
         <v>62.2</v>
       </c>
       <c r="M41">
-        <v>5.8626204</v>
+        <v>6.012944</v>
       </c>
       <c r="N41">
-        <v>56.33737960000001</v>
+        <v>56.18705600000001</v>
       </c>
       <c r="O41">
-        <v>16.90121388</v>
+        <v>16.8561168</v>
       </c>
       <c r="P41">
-        <v>39.43616572000001</v>
+        <v>39.3309392</v>
       </c>
       <c r="Q41">
-        <v>44.93616572000001</v>
+        <v>44.8309392</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1614957393233739</v>
+        <v>0.1630243731007684</v>
       </c>
       <c r="T41">
-        <v>0.8066818962726773</v>
+        <v>0.8173402074729581</v>
       </c>
       <c r="U41">
         <v>0.0518</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>10.60959020986588</v>
+        <v>10.34435045461924</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.112318623860461</v>
+        <v>0.111983446733664</v>
       </c>
       <c r="C42">
-        <v>205.6619330057001</v>
+        <v>203.6365709581083</v>
       </c>
       <c r="D42">
-        <v>321.7419330057</v>
+        <v>322.6185709581083</v>
       </c>
       <c r="E42">
-        <v>116.08</v>
+        <v>118.982</v>
       </c>
       <c r="F42">
-        <v>116.08</v>
+        <v>118.982</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -4731,28 +4731,28 @@
         <v>62.2</v>
       </c>
       <c r="M42">
-        <v>6.012944</v>
+        <v>6.1632676</v>
       </c>
       <c r="N42">
-        <v>56.18705600000001</v>
+        <v>56.03673240000001</v>
       </c>
       <c r="O42">
-        <v>16.8561168</v>
+        <v>16.81101972</v>
       </c>
       <c r="P42">
-        <v>39.3309392</v>
+        <v>39.22571268</v>
       </c>
       <c r="Q42">
-        <v>44.8309392</v>
+        <v>44.72571268</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1630243731007684</v>
+        <v>0.1646048249723119</v>
       </c>
       <c r="T42">
-        <v>0.8173402074729581</v>
+        <v>0.8283598173579941</v>
       </c>
       <c r="U42">
         <v>0.0518</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>10.34435045461924</v>
+        <v>10.09204922401877</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.111983446733664</v>
+        <v>0.111648269606867</v>
       </c>
       <c r="C43">
-        <v>203.6365709581083</v>
+        <v>201.6159990458878</v>
       </c>
       <c r="D43">
-        <v>322.6185709581083</v>
+        <v>323.4999990458878</v>
       </c>
       <c r="E43">
-        <v>118.982</v>
+        <v>121.884</v>
       </c>
       <c r="F43">
-        <v>118.982</v>
+        <v>121.884</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -4813,28 +4813,28 @@
         <v>62.2</v>
       </c>
       <c r="M43">
-        <v>6.1632676</v>
+        <v>6.3135912</v>
       </c>
       <c r="N43">
-        <v>56.03673240000001</v>
+        <v>55.88640880000001</v>
       </c>
       <c r="O43">
-        <v>16.81101972</v>
+        <v>16.76592264</v>
       </c>
       <c r="P43">
-        <v>39.22571268</v>
+        <v>39.12048616000001</v>
       </c>
       <c r="Q43">
-        <v>44.72571268</v>
+        <v>44.62048616000001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1646048249723119</v>
+        <v>0.1662397751842534</v>
       </c>
       <c r="T43">
-        <v>0.8283598173579941</v>
+        <v>0.83975941379079</v>
       </c>
       <c r="U43">
         <v>0.0518</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>10.09204922401877</v>
+        <v>9.851762337732605</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.111648269606867</v>
+        <v>0.1118247924800699</v>
       </c>
       <c r="C44">
-        <v>201.6159990458878</v>
+        <v>198.2491906412603</v>
       </c>
       <c r="D44">
-        <v>323.4999990458878</v>
+        <v>323.0351906412603</v>
       </c>
       <c r="E44">
-        <v>121.884</v>
+        <v>124.786</v>
       </c>
       <c r="F44">
-        <v>121.884</v>
+        <v>124.786</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -4895,45 +4895,45 @@
         <v>62.2</v>
       </c>
       <c r="M44">
-        <v>6.313591199999999</v>
+        <v>6.676050999999999</v>
       </c>
       <c r="N44">
-        <v>55.88640880000001</v>
+        <v>55.523949</v>
       </c>
       <c r="O44">
-        <v>16.76592264</v>
+        <v>16.6571847</v>
       </c>
       <c r="P44">
-        <v>39.12048616000001</v>
+        <v>38.8667643</v>
       </c>
       <c r="Q44">
-        <v>44.62048616000001</v>
+        <v>44.3667643</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1662397751842534</v>
+        <v>0.1679320920702981</v>
       </c>
       <c r="T44">
-        <v>0.8397594137907899</v>
+        <v>0.8515589960633331</v>
       </c>
       <c r="U44">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V44">
         <v>0.3</v>
       </c>
       <c r="W44">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y44">
-        <v>9.851762337732605</v>
+        <v>9.316885086707696</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1118247924800699</v>
+        <v>0.1115015153532729</v>
       </c>
       <c r="C45">
-        <v>198.2491906412603</v>
+        <v>196.1994421686688</v>
       </c>
       <c r="D45">
-        <v>323.0351906412603</v>
+        <v>323.8874421686688</v>
       </c>
       <c r="E45">
-        <v>124.786</v>
+        <v>127.688</v>
       </c>
       <c r="F45">
-        <v>124.786</v>
+        <v>127.688</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -4977,28 +4977,28 @@
         <v>62.2</v>
       </c>
       <c r="M45">
-        <v>6.676050999999999</v>
+        <v>6.831308</v>
       </c>
       <c r="N45">
-        <v>55.523949</v>
+        <v>55.368692</v>
       </c>
       <c r="O45">
-        <v>16.6571847</v>
+        <v>16.6106076</v>
       </c>
       <c r="P45">
-        <v>38.8667643</v>
+        <v>38.7580844</v>
       </c>
       <c r="Q45">
-        <v>44.3667643</v>
+        <v>44.2580844</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1679320920702981</v>
+        <v>0.1696848488451302</v>
       </c>
       <c r="T45">
-        <v>0.8515589960633331</v>
+        <v>0.8637799919884669</v>
       </c>
       <c r="U45">
         <v>0.0535</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>9.316885086707696</v>
+        <v>9.105137698373431</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1115015153532729</v>
+        <v>0.1111782382264759</v>
       </c>
       <c r="C46">
-        <v>196.1994421686688</v>
+        <v>194.1542025174813</v>
       </c>
       <c r="D46">
-        <v>323.8874421686688</v>
+        <v>324.7442025174813</v>
       </c>
       <c r="E46">
-        <v>127.688</v>
+        <v>130.59</v>
       </c>
       <c r="F46">
-        <v>127.688</v>
+        <v>130.59</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -5059,28 +5059,28 @@
         <v>62.2</v>
       </c>
       <c r="M46">
-        <v>6.831308</v>
+        <v>6.986565</v>
       </c>
       <c r="N46">
-        <v>55.368692</v>
+        <v>55.213435</v>
       </c>
       <c r="O46">
-        <v>16.6106076</v>
+        <v>16.5640305</v>
       </c>
       <c r="P46">
-        <v>38.7580844</v>
+        <v>38.6494045</v>
       </c>
       <c r="Q46">
-        <v>44.2580844</v>
+        <v>44.1494045</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1696848488451302</v>
+        <v>0.1715013422299562</v>
       </c>
       <c r="T46">
-        <v>0.8637799919884669</v>
+        <v>0.876445387765424</v>
       </c>
       <c r="U46">
         <v>0.0535</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>9.105137698373431</v>
+        <v>8.902801305076244</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1111782382264759</v>
+        <v>0.1108549610996789</v>
       </c>
       <c r="C47">
-        <v>194.1542025174813</v>
+        <v>192.1135075633559</v>
       </c>
       <c r="D47">
-        <v>324.7442025174813</v>
+        <v>325.6055075633559</v>
       </c>
       <c r="E47">
-        <v>130.59</v>
+        <v>133.492</v>
       </c>
       <c r="F47">
-        <v>130.59</v>
+        <v>133.492</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -5141,28 +5141,28 @@
         <v>62.2</v>
       </c>
       <c r="M47">
-        <v>6.986565</v>
+        <v>7.141821999999999</v>
       </c>
       <c r="N47">
-        <v>55.213435</v>
+        <v>55.05817800000001</v>
       </c>
       <c r="O47">
-        <v>16.5640305</v>
+        <v>16.5174534</v>
       </c>
       <c r="P47">
-        <v>38.6494045</v>
+        <v>38.5407246</v>
       </c>
       <c r="Q47">
-        <v>44.1494045</v>
+        <v>44.0407246</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1715013422299562</v>
+        <v>0.1733851131475534</v>
       </c>
       <c r="T47">
-        <v>0.876445387765424</v>
+        <v>0.8895798722748608</v>
       </c>
       <c r="U47">
         <v>0.0535</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>8.902801305076244</v>
+        <v>8.709262146270238</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1108549610996789</v>
+        <v>0.1105316839728819</v>
       </c>
       <c r="C48">
-        <v>192.1135075633559</v>
+        <v>190.0773935635682</v>
       </c>
       <c r="D48">
-        <v>325.6055075633559</v>
+        <v>326.4713935635682</v>
       </c>
       <c r="E48">
-        <v>133.492</v>
+        <v>136.394</v>
       </c>
       <c r="F48">
-        <v>133.492</v>
+        <v>136.394</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -5223,28 +5223,28 @@
         <v>62.2</v>
       </c>
       <c r="M48">
-        <v>7.141821999999999</v>
+        <v>7.297079</v>
       </c>
       <c r="N48">
-        <v>55.05817800000001</v>
+        <v>54.90292100000001</v>
       </c>
       <c r="O48">
-        <v>16.5174534</v>
+        <v>16.4708763</v>
       </c>
       <c r="P48">
-        <v>38.5407246</v>
+        <v>38.43204470000001</v>
       </c>
       <c r="Q48">
-        <v>44.0407246</v>
+        <v>43.93204470000001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1733851131475534</v>
+        <v>0.1753399697601544</v>
       </c>
       <c r="T48">
-        <v>0.8895798722748608</v>
+        <v>0.9032099977091822</v>
       </c>
       <c r="U48">
         <v>0.0535</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>8.709262146270238</v>
+        <v>8.523958696349595</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1105316839728819</v>
+        <v>0.1102084068460848</v>
       </c>
       <c r="C49">
-        <v>190.0773935635682</v>
+        <v>188.0458971620998</v>
       </c>
       <c r="D49">
-        <v>326.4713935635682</v>
+        <v>327.3418971620998</v>
       </c>
       <c r="E49">
-        <v>136.394</v>
+        <v>139.296</v>
       </c>
       <c r="F49">
-        <v>136.394</v>
+        <v>139.296</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -5305,28 +5305,28 @@
         <v>62.2</v>
       </c>
       <c r="M49">
-        <v>7.297079</v>
+        <v>7.452336</v>
       </c>
       <c r="N49">
-        <v>54.90292100000001</v>
+        <v>54.747664</v>
       </c>
       <c r="O49">
-        <v>16.4708763</v>
+        <v>16.4242992</v>
       </c>
       <c r="P49">
-        <v>38.43204470000001</v>
+        <v>38.3233648</v>
       </c>
       <c r="Q49">
-        <v>43.93204470000001</v>
+        <v>43.8233648</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1753399697601544</v>
+        <v>0.1773700131655477</v>
       </c>
       <c r="T49">
-        <v>0.9032099977091822</v>
+        <v>0.9173643587371312</v>
       </c>
       <c r="U49">
         <v>0.0535</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>8.523958696349595</v>
+        <v>8.346376223508978</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1102084068460848</v>
+        <v>0.1098851297192878</v>
       </c>
       <c r="C50">
-        <v>188.0458971620998</v>
+        <v>186.0190553948072</v>
       </c>
       <c r="D50">
-        <v>327.3418971620998</v>
+        <v>328.2170553948072</v>
       </c>
       <c r="E50">
-        <v>139.296</v>
+        <v>142.198</v>
       </c>
       <c r="F50">
-        <v>139.296</v>
+        <v>142.198</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -5387,28 +5387,28 @@
         <v>62.2</v>
       </c>
       <c r="M50">
-        <v>7.452336</v>
+        <v>7.607592999999999</v>
       </c>
       <c r="N50">
-        <v>54.747664</v>
+        <v>54.592407</v>
       </c>
       <c r="O50">
-        <v>16.4242992</v>
+        <v>16.3777221</v>
       </c>
       <c r="P50">
-        <v>38.3233648</v>
+        <v>38.2146849</v>
       </c>
       <c r="Q50">
-        <v>43.8233648</v>
+        <v>43.7146849</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1773700131655477</v>
+        <v>0.1794796661162506</v>
       </c>
       <c r="T50">
-        <v>0.9173643587371312</v>
+        <v>0.9320737927465684</v>
       </c>
       <c r="U50">
         <v>0.0535</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>8.346376223508978</v>
+        <v>8.176042014865939</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1098851297192878</v>
+        <v>0.1095618525924908</v>
       </c>
       <c r="C51">
-        <v>186.0190553948072</v>
+        <v>183.9969056946745</v>
       </c>
       <c r="D51">
-        <v>328.2170553948072</v>
+        <v>329.0969056946745</v>
       </c>
       <c r="E51">
-        <v>142.198</v>
+        <v>145.1</v>
       </c>
       <c r="F51">
-        <v>142.198</v>
+        <v>145.1</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -5469,28 +5469,28 @@
         <v>62.2</v>
       </c>
       <c r="M51">
-        <v>7.607592999999999</v>
+        <v>7.762849999999999</v>
       </c>
       <c r="N51">
-        <v>54.592407</v>
+        <v>54.43715</v>
       </c>
       <c r="O51">
-        <v>16.3777221</v>
+        <v>16.331145</v>
       </c>
       <c r="P51">
-        <v>38.2146849</v>
+        <v>38.106005</v>
       </c>
       <c r="Q51">
-        <v>43.7146849</v>
+        <v>43.606005</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1794796661162506</v>
+        <v>0.1816737051849815</v>
       </c>
       <c r="T51">
-        <v>0.9320737927465684</v>
+        <v>0.9473716041163832</v>
       </c>
       <c r="U51">
         <v>0.0535</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>8.176042014865939</v>
+        <v>8.012521174568619</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1095618525924908</v>
+        <v>0.1092385754656937</v>
       </c>
       <c r="C52">
-        <v>183.9969056946745</v>
+        <v>181.9794858971508</v>
       </c>
       <c r="D52">
-        <v>329.0969056946745</v>
+        <v>329.9814858971508</v>
       </c>
       <c r="E52">
-        <v>145.1</v>
+        <v>148.002</v>
       </c>
       <c r="F52">
-        <v>145.1</v>
+        <v>148.002</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -5551,28 +5551,28 @@
         <v>62.2</v>
       </c>
       <c r="M52">
-        <v>7.762849999999999</v>
+        <v>7.918107</v>
       </c>
       <c r="N52">
-        <v>54.43715</v>
+        <v>54.281893</v>
       </c>
       <c r="O52">
-        <v>16.331145</v>
+        <v>16.2845679</v>
       </c>
       <c r="P52">
-        <v>38.106005</v>
+        <v>37.9973251</v>
       </c>
       <c r="Q52">
-        <v>43.606005</v>
+        <v>43.4973251</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1816737051849815</v>
+        <v>0.1839572968687627</v>
       </c>
       <c r="T52">
-        <v>0.9473716041163832</v>
+        <v>0.9632938159502721</v>
       </c>
       <c r="U52">
         <v>0.0535</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>8.012521174568619</v>
+        <v>7.855412916243744</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1092385754656937</v>
+        <v>0.1089152983388967</v>
       </c>
       <c r="C53">
-        <v>181.9794858971508</v>
+        <v>179.966834245573</v>
       </c>
       <c r="D53">
-        <v>329.9814858971508</v>
+        <v>330.870834245573</v>
       </c>
       <c r="E53">
-        <v>148.002</v>
+        <v>150.904</v>
       </c>
       <c r="F53">
-        <v>148.002</v>
+        <v>150.904</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -5633,28 +5633,28 @@
         <v>62.2</v>
       </c>
       <c r="M53">
-        <v>7.918107</v>
+        <v>8.073364</v>
       </c>
       <c r="N53">
-        <v>54.281893</v>
+        <v>54.126636</v>
       </c>
       <c r="O53">
-        <v>16.2845679</v>
+        <v>16.2379908</v>
       </c>
       <c r="P53">
-        <v>37.9973251</v>
+        <v>37.8886452</v>
       </c>
       <c r="Q53">
-        <v>43.4973251</v>
+        <v>43.3886452</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1839572968687627</v>
+        <v>0.1863360382060348</v>
       </c>
       <c r="T53">
-        <v>0.9632938159502721</v>
+        <v>0.9798794532772395</v>
       </c>
       <c r="U53">
         <v>0.0535</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>7.855412916243744</v>
+        <v>7.704347283239057</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1089152983388967</v>
+        <v>0.1088888212120997</v>
       </c>
       <c r="C54">
-        <v>179.966834245573</v>
+        <v>177.1378863227621</v>
       </c>
       <c r="D54">
-        <v>330.870834245573</v>
+        <v>330.9438863227621</v>
       </c>
       <c r="E54">
-        <v>150.904</v>
+        <v>153.806</v>
       </c>
       <c r="F54">
-        <v>150.904</v>
+        <v>153.806</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -5715,45 +5715,45 @@
         <v>62.2</v>
       </c>
       <c r="M54">
-        <v>8.073364</v>
+        <v>8.351665800000001</v>
       </c>
       <c r="N54">
-        <v>54.126636</v>
+        <v>53.8483342</v>
       </c>
       <c r="O54">
-        <v>16.2379908</v>
+        <v>16.15450026</v>
       </c>
       <c r="P54">
-        <v>37.8886452</v>
+        <v>37.69383394</v>
       </c>
       <c r="Q54">
-        <v>43.3886452</v>
+        <v>43.19383394</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1863360382060348</v>
+        <v>0.1888160025789355</v>
       </c>
       <c r="T54">
-        <v>0.9798794532772395</v>
+        <v>0.9971708624053546</v>
       </c>
       <c r="U54">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V54">
         <v>0.3</v>
       </c>
       <c r="W54">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y54">
-        <v>7.704347283239057</v>
+        <v>7.447616019309584</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1088888212120997</v>
+        <v>0.1085711440853026</v>
       </c>
       <c r="C55">
-        <v>177.1378863227621</v>
+        <v>175.1148997883138</v>
       </c>
       <c r="D55">
-        <v>330.9438863227621</v>
+        <v>331.8228997883138</v>
       </c>
       <c r="E55">
-        <v>153.806</v>
+        <v>156.708</v>
       </c>
       <c r="F55">
-        <v>153.806</v>
+        <v>156.708</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -5797,28 +5797,28 @@
         <v>62.2</v>
       </c>
       <c r="M55">
-        <v>8.351665800000001</v>
+        <v>8.5092444</v>
       </c>
       <c r="N55">
-        <v>53.8483342</v>
+        <v>53.6907556</v>
       </c>
       <c r="O55">
-        <v>16.15450026</v>
+        <v>16.10722668</v>
       </c>
       <c r="P55">
-        <v>37.69383394</v>
+        <v>37.58352892000001</v>
       </c>
       <c r="Q55">
-        <v>43.19383394</v>
+        <v>43.08352892000001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1888160025789355</v>
+        <v>0.1914037914897884</v>
       </c>
       <c r="T55">
-        <v>0.9971708624053546</v>
+        <v>1.015214071930344</v>
       </c>
       <c r="U55">
         <v>0.0543</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>7.447616019309584</v>
+        <v>7.309697204137185</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1085711440853026</v>
+        <v>0.1082534669585056</v>
       </c>
       <c r="C56">
-        <v>175.1148997883138</v>
+        <v>173.0965951496754</v>
       </c>
       <c r="D56">
-        <v>331.8228997883138</v>
+        <v>332.7065951496754</v>
       </c>
       <c r="E56">
-        <v>156.708</v>
+        <v>159.61</v>
       </c>
       <c r="F56">
-        <v>156.708</v>
+        <v>159.61</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -5879,28 +5879,28 @@
         <v>62.2</v>
       </c>
       <c r="M56">
-        <v>8.5092444</v>
+        <v>8.666823000000001</v>
       </c>
       <c r="N56">
-        <v>53.6907556</v>
+        <v>53.533177</v>
       </c>
       <c r="O56">
-        <v>16.10722668</v>
+        <v>16.0599531</v>
       </c>
       <c r="P56">
-        <v>37.58352892000001</v>
+        <v>37.4732239</v>
       </c>
       <c r="Q56">
-        <v>43.08352892000001</v>
+        <v>42.9732239</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1914037914897884</v>
+        <v>0.1941065932411236</v>
       </c>
       <c r="T56">
-        <v>1.015214071930344</v>
+        <v>1.034059201878667</v>
       </c>
       <c r="U56">
         <v>0.0543</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>7.309697204137185</v>
+        <v>7.176793618607418</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1082534669585056</v>
+        <v>0.1079357898317086</v>
       </c>
       <c r="C57">
-        <v>173.0965951496754</v>
+        <v>171.083009912554</v>
       </c>
       <c r="D57">
-        <v>332.7065951496754</v>
+        <v>333.595009912554</v>
       </c>
       <c r="E57">
-        <v>159.61</v>
+        <v>162.512</v>
       </c>
       <c r="F57">
-        <v>159.61</v>
+        <v>162.512</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -5961,28 +5961,28 @@
         <v>62.2</v>
       </c>
       <c r="M57">
-        <v>8.666823000000001</v>
+        <v>8.8244016</v>
       </c>
       <c r="N57">
-        <v>53.533177</v>
+        <v>53.3755984</v>
       </c>
       <c r="O57">
-        <v>16.0599531</v>
+        <v>16.01267952</v>
       </c>
       <c r="P57">
-        <v>37.4732239</v>
+        <v>37.36291888</v>
       </c>
       <c r="Q57">
-        <v>42.9732239</v>
+        <v>42.86291888</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1941065932411236</v>
+        <v>0.1969322496175196</v>
       </c>
       <c r="T57">
-        <v>1.034059201878667</v>
+        <v>1.053760928642822</v>
       </c>
       <c r="U57">
         <v>0.0543</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>7.176793618607418</v>
+        <v>7.048636589703714</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1079357898317086</v>
+        <v>0.1076181127049116</v>
       </c>
       <c r="C58">
-        <v>171.083009912554</v>
+        <v>169.0741819843298</v>
       </c>
       <c r="D58">
-        <v>333.595009912554</v>
+        <v>334.4881819843298</v>
       </c>
       <c r="E58">
-        <v>162.512</v>
+        <v>165.414</v>
       </c>
       <c r="F58">
-        <v>162.512</v>
+        <v>165.414</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -6043,28 +6043,28 @@
         <v>62.2</v>
       </c>
       <c r="M58">
-        <v>8.8244016</v>
+        <v>8.981980200000001</v>
       </c>
       <c r="N58">
-        <v>53.3755984</v>
+        <v>53.2180198</v>
       </c>
       <c r="O58">
-        <v>16.01267952</v>
+        <v>15.96540594</v>
       </c>
       <c r="P58">
-        <v>37.36291888</v>
+        <v>37.25261386</v>
       </c>
       <c r="Q58">
-        <v>42.86291888</v>
+        <v>42.75261386</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1969322496175196</v>
+        <v>0.1998893318718874</v>
       </c>
       <c r="T58">
-        <v>1.053760928642822</v>
+        <v>1.074379014791357</v>
       </c>
       <c r="U58">
         <v>0.0543</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>7.048636589703714</v>
+        <v>6.92497629865628</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1076181127049116</v>
+        <v>0.1073004355781145</v>
       </c>
       <c r="C59">
-        <v>169.0741819843298</v>
+        <v>167.0701496794479</v>
       </c>
       <c r="D59">
-        <v>334.4881819843298</v>
+        <v>335.3861496794479</v>
       </c>
       <c r="E59">
-        <v>165.414</v>
+        <v>168.316</v>
       </c>
       <c r="F59">
-        <v>165.414</v>
+        <v>168.316</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -6125,28 +6125,28 @@
         <v>62.2</v>
       </c>
       <c r="M59">
-        <v>8.981980200000001</v>
+        <v>9.1395588</v>
       </c>
       <c r="N59">
-        <v>53.2180198</v>
+        <v>53.0604412</v>
       </c>
       <c r="O59">
-        <v>15.96540594</v>
+        <v>15.91813236</v>
       </c>
       <c r="P59">
-        <v>37.25261386</v>
+        <v>37.14230884</v>
       </c>
       <c r="Q59">
-        <v>42.75261386</v>
+        <v>42.64230884</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1998893318718874</v>
+        <v>0.2029872275669394</v>
       </c>
       <c r="T59">
-        <v>1.074379014791357</v>
+        <v>1.095978914566012</v>
       </c>
       <c r="U59">
         <v>0.0543</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>6.92497629865628</v>
+        <v>6.805580155576</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1073004355781146</v>
+        <v>0.1069827584513175</v>
       </c>
       <c r="C60">
-        <v>167.0701496794479</v>
+        <v>165.0709517248973</v>
       </c>
       <c r="D60">
-        <v>335.3861496794478</v>
+        <v>336.2889517248973</v>
       </c>
       <c r="E60">
-        <v>168.316</v>
+        <v>171.218</v>
       </c>
       <c r="F60">
-        <v>168.316</v>
+        <v>171.218</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -6207,28 +6207,28 @@
         <v>62.2</v>
       </c>
       <c r="M60">
-        <v>9.1395588</v>
+        <v>9.2971374</v>
       </c>
       <c r="N60">
-        <v>53.0604412</v>
+        <v>52.90286260000001</v>
       </c>
       <c r="O60">
-        <v>15.91813236</v>
+        <v>15.87085878</v>
       </c>
       <c r="P60">
-        <v>37.14230884</v>
+        <v>37.03200382000001</v>
       </c>
       <c r="Q60">
-        <v>42.64230884</v>
+        <v>42.53200382000001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2029872275669394</v>
+        <v>0.2062362401251647</v>
       </c>
       <c r="T60">
-        <v>1.095978914566012</v>
+        <v>1.118632467988211</v>
       </c>
       <c r="U60">
         <v>0.0543</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>6.805580155576</v>
+        <v>6.690231339379797</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1069827584513175</v>
+        <v>0.1066650813245205</v>
       </c>
       <c r="C61">
-        <v>165.0709517248973</v>
+        <v>163.0766272657779</v>
       </c>
       <c r="D61">
-        <v>336.2889517248973</v>
+        <v>337.1966272657779</v>
       </c>
       <c r="E61">
-        <v>171.218</v>
+        <v>174.12</v>
       </c>
       <c r="F61">
-        <v>171.218</v>
+        <v>174.12</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -6289,28 +6289,28 @@
         <v>62.2</v>
       </c>
       <c r="M61">
-        <v>9.2971374</v>
+        <v>9.454715999999999</v>
       </c>
       <c r="N61">
-        <v>52.90286260000001</v>
+        <v>52.74528400000001</v>
       </c>
       <c r="O61">
-        <v>15.87085878</v>
+        <v>15.8235852</v>
       </c>
       <c r="P61">
-        <v>37.03200382000001</v>
+        <v>36.9216988</v>
       </c>
       <c r="Q61">
-        <v>42.53200382000001</v>
+        <v>42.4216988</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2062362401251647</v>
+        <v>0.2096477033113013</v>
       </c>
       <c r="T61">
-        <v>1.118632467988211</v>
+        <v>1.142418699081521</v>
       </c>
       <c r="U61">
         <v>0.0543</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>6.690231339379797</v>
+        <v>6.578727483723467</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1066650813245205</v>
+        <v>0.1063474041977235</v>
       </c>
       <c r="C62">
-        <v>163.0766272657779</v>
+        <v>161.0872158709589</v>
       </c>
       <c r="D62">
-        <v>337.1966272657779</v>
+        <v>338.1092158709589</v>
       </c>
       <c r="E62">
-        <v>174.12</v>
+        <v>177.022</v>
       </c>
       <c r="F62">
-        <v>174.12</v>
+        <v>177.022</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -6371,28 +6371,28 @@
         <v>62.2</v>
       </c>
       <c r="M62">
-        <v>9.454715999999999</v>
+        <v>9.6122946</v>
       </c>
       <c r="N62">
-        <v>52.74528400000001</v>
+        <v>52.5877054</v>
       </c>
       <c r="O62">
-        <v>15.8235852</v>
+        <v>15.77631162</v>
       </c>
       <c r="P62">
-        <v>36.9216988</v>
+        <v>36.81139378</v>
       </c>
       <c r="Q62">
-        <v>42.4216988</v>
+        <v>42.31139378</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2096477033113013</v>
+        <v>0.2132341133274961</v>
       </c>
       <c r="T62">
-        <v>1.142418699081521</v>
+        <v>1.167424736897564</v>
       </c>
       <c r="U62">
         <v>0.0543</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>6.578727483723467</v>
+        <v>6.470879492187017</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1063474041977235</v>
+        <v>0.1060297270709264</v>
       </c>
       <c r="C63">
-        <v>161.0872158709589</v>
+        <v>159.1027575388285</v>
       </c>
       <c r="D63">
-        <v>338.1092158709589</v>
+        <v>339.0267575388285</v>
       </c>
       <c r="E63">
-        <v>177.022</v>
+        <v>179.924</v>
       </c>
       <c r="F63">
-        <v>177.022</v>
+        <v>179.924</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -6453,28 +6453,28 @@
         <v>62.2</v>
       </c>
       <c r="M63">
-        <v>9.6122946</v>
+        <v>9.769873199999999</v>
       </c>
       <c r="N63">
-        <v>52.5877054</v>
+        <v>52.4301268</v>
       </c>
       <c r="O63">
-        <v>15.77631162</v>
+        <v>15.72903804</v>
       </c>
       <c r="P63">
-        <v>36.81139378</v>
+        <v>36.70108876</v>
       </c>
       <c r="Q63">
-        <v>42.31139378</v>
+        <v>42.20108876</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2132341133274961</v>
+        <v>0.2170092817655959</v>
       </c>
       <c r="T63">
-        <v>1.167424736897564</v>
+        <v>1.193746881967083</v>
       </c>
       <c r="U63">
         <v>0.0543</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>6.470879492187017</v>
+        <v>6.366510468119484</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1060297270709264</v>
+        <v>0.1057120499441294</v>
       </c>
       <c r="C64">
-        <v>159.1027575388285</v>
+        <v>157.1232927031374</v>
       </c>
       <c r="D64">
-        <v>339.0267575388285</v>
+        <v>339.9492927031374</v>
       </c>
       <c r="E64">
-        <v>179.924</v>
+        <v>182.826</v>
       </c>
       <c r="F64">
-        <v>179.924</v>
+        <v>182.826</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -6535,28 +6535,28 @@
         <v>62.2</v>
       </c>
       <c r="M64">
-        <v>9.769873199999999</v>
+        <v>9.9274518</v>
       </c>
       <c r="N64">
-        <v>52.4301268</v>
+        <v>52.2725482</v>
       </c>
       <c r="O64">
-        <v>15.72903804</v>
+        <v>15.68176446</v>
       </c>
       <c r="P64">
-        <v>36.70108876</v>
+        <v>36.59078374000001</v>
       </c>
       <c r="Q64">
-        <v>42.20108876</v>
+        <v>42.09078374000001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2170092817655959</v>
+        <v>0.220988513362512</v>
       </c>
       <c r="T64">
-        <v>1.193746881967083</v>
+        <v>1.221491845689009</v>
       </c>
       <c r="U64">
         <v>0.0543</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>6.366510468119484</v>
+        <v>6.265454746403302</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1057120499441294</v>
+        <v>0.1053943728173324</v>
       </c>
       <c r="C65">
-        <v>157.1232927031374</v>
+        <v>155.1488622389393</v>
       </c>
       <c r="D65">
-        <v>339.9492927031374</v>
+        <v>340.8768622389393</v>
       </c>
       <c r="E65">
-        <v>182.826</v>
+        <v>185.728</v>
       </c>
       <c r="F65">
-        <v>182.826</v>
+        <v>185.728</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -6617,28 +6617,28 @@
         <v>62.2</v>
       </c>
       <c r="M65">
-        <v>9.9274518</v>
+        <v>10.0850304</v>
       </c>
       <c r="N65">
-        <v>52.2725482</v>
+        <v>52.1149696</v>
       </c>
       <c r="O65">
-        <v>15.68176446</v>
+        <v>15.63449088</v>
       </c>
       <c r="P65">
-        <v>36.59078374000001</v>
+        <v>36.48047872</v>
       </c>
       <c r="Q65">
-        <v>42.09078374000001</v>
+        <v>41.98047872</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.220988513362512</v>
+        <v>0.2251888133814789</v>
       </c>
       <c r="T65">
-        <v>1.221491845689009</v>
+        <v>1.250778196284375</v>
       </c>
       <c r="U65">
         <v>0.0543</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>6.265454746403302</v>
+        <v>6.16755701599075</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1053943728173324</v>
+        <v>0.1055316956905354</v>
       </c>
       <c r="C66">
-        <v>155.1488622389393</v>
+        <v>151.8452796682734</v>
       </c>
       <c r="D66">
-        <v>340.8768622389393</v>
+        <v>340.4752796682734</v>
       </c>
       <c r="E66">
-        <v>185.728</v>
+        <v>188.63</v>
       </c>
       <c r="F66">
-        <v>185.728</v>
+        <v>188.63</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -6699,45 +6699,45 @@
         <v>62.2</v>
       </c>
       <c r="M66">
-        <v>10.0850304</v>
+        <v>10.431239</v>
       </c>
       <c r="N66">
-        <v>52.1149696</v>
+        <v>51.768761</v>
       </c>
       <c r="O66">
-        <v>15.63449088</v>
+        <v>15.5306283</v>
       </c>
       <c r="P66">
-        <v>36.48047872</v>
+        <v>36.23813270000001</v>
       </c>
       <c r="Q66">
-        <v>41.98047872</v>
+        <v>41.73813270000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2251888133814789</v>
+        <v>0.2296291305443867</v>
       </c>
       <c r="T66">
-        <v>1.250778196284375</v>
+        <v>1.281738052628048</v>
       </c>
       <c r="U66">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V66">
         <v>0.3</v>
       </c>
       <c r="W66">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y66">
-        <v>6.16755701599075</v>
+        <v>5.962858295165129</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1055316956905354</v>
+        <v>0.1052210185637383</v>
       </c>
       <c r="C67">
-        <v>151.8452796682734</v>
+        <v>149.8531685950462</v>
       </c>
       <c r="D67">
-        <v>340.4752796682734</v>
+        <v>341.3851685950463</v>
       </c>
       <c r="E67">
-        <v>188.63</v>
+        <v>191.532</v>
       </c>
       <c r="F67">
-        <v>188.63</v>
+        <v>191.532</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -6781,28 +6781,28 @@
         <v>62.2</v>
       </c>
       <c r="M67">
-        <v>10.431239</v>
+        <v>10.5917196</v>
       </c>
       <c r="N67">
-        <v>51.768761</v>
+        <v>51.6082804</v>
       </c>
       <c r="O67">
-        <v>15.5306283</v>
+        <v>15.48248412</v>
       </c>
       <c r="P67">
-        <v>36.23813270000001</v>
+        <v>36.12579628</v>
       </c>
       <c r="Q67">
-        <v>41.73813270000001</v>
+        <v>41.62579628</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2296291305443867</v>
+        <v>0.2343306428345245</v>
       </c>
       <c r="T67">
-        <v>1.281738052628048</v>
+        <v>1.314519076991937</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.962858295165129</v>
+        <v>5.872511957359595</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1052210185637383</v>
+        <v>0.1049103414369413</v>
       </c>
       <c r="C68">
-        <v>149.8531685950462</v>
+        <v>147.8659337423153</v>
       </c>
       <c r="D68">
-        <v>341.3851685950463</v>
+        <v>342.2999337423153</v>
       </c>
       <c r="E68">
-        <v>191.532</v>
+        <v>194.434</v>
       </c>
       <c r="F68">
-        <v>191.532</v>
+        <v>194.434</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -6863,28 +6863,28 @@
         <v>62.2</v>
       </c>
       <c r="M68">
-        <v>10.5917196</v>
+        <v>10.7522002</v>
       </c>
       <c r="N68">
-        <v>51.6082804</v>
+        <v>51.4477998</v>
       </c>
       <c r="O68">
-        <v>15.48248412</v>
+        <v>15.43433994</v>
       </c>
       <c r="P68">
-        <v>36.12579628</v>
+        <v>36.01345986</v>
       </c>
       <c r="Q68">
-        <v>41.62579628</v>
+        <v>41.51345986</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2343306428345245</v>
+        <v>0.2393170952634586</v>
       </c>
       <c r="T68">
-        <v>1.314519076991937</v>
+        <v>1.349286830105152</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>5.872511957359595</v>
+        <v>5.784862525160198</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1049103414369413</v>
+        <v>0.1045996643101443</v>
       </c>
       <c r="C69">
-        <v>147.8659337423153</v>
+        <v>145.8836144139071</v>
       </c>
       <c r="D69">
-        <v>342.2999337423153</v>
+        <v>343.2196144139071</v>
       </c>
       <c r="E69">
-        <v>194.434</v>
+        <v>197.336</v>
       </c>
       <c r="F69">
-        <v>194.434</v>
+        <v>197.336</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -6945,28 +6945,28 @@
         <v>62.2</v>
       </c>
       <c r="M69">
-        <v>10.7522002</v>
+        <v>10.9126808</v>
       </c>
       <c r="N69">
-        <v>51.4477998</v>
+        <v>51.2873192</v>
       </c>
       <c r="O69">
-        <v>15.43433994</v>
+        <v>15.38619576</v>
       </c>
       <c r="P69">
-        <v>36.01345986</v>
+        <v>35.90112344</v>
       </c>
       <c r="Q69">
-        <v>41.51345986</v>
+        <v>41.40112344</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2393170952634586</v>
+        <v>0.2446152009692009</v>
       </c>
       <c r="T69">
-        <v>1.349286830105152</v>
+        <v>1.386227567787943</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>5.784862525160198</v>
+        <v>5.699791017437255</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1045996643101443</v>
+        <v>0.1042889871833473</v>
       </c>
       <c r="C70">
-        <v>145.8836144139071</v>
+        <v>143.9062503371873</v>
       </c>
       <c r="D70">
-        <v>343.2196144139071</v>
+        <v>344.1442503371873</v>
       </c>
       <c r="E70">
-        <v>197.336</v>
+        <v>200.238</v>
       </c>
       <c r="F70">
-        <v>197.336</v>
+        <v>200.238</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -7027,28 +7027,28 @@
         <v>62.2</v>
       </c>
       <c r="M70">
-        <v>10.9126808</v>
+        <v>11.0731614</v>
       </c>
       <c r="N70">
-        <v>51.2873192</v>
+        <v>51.1268386</v>
       </c>
       <c r="O70">
-        <v>15.38619576</v>
+        <v>15.33805158</v>
       </c>
       <c r="P70">
-        <v>35.90112344</v>
+        <v>35.78878702</v>
       </c>
       <c r="Q70">
-        <v>41.40112344</v>
+        <v>41.28878702</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2446152009692009</v>
+        <v>0.2502551199462815</v>
       </c>
       <c r="T70">
-        <v>1.386227567787943</v>
+        <v>1.425551578869624</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>5.699791017437255</v>
+        <v>5.617185350517874</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1042889871833473</v>
+        <v>0.1039783100565502</v>
       </c>
       <c r="C71">
-        <v>143.9062503371873</v>
+        <v>141.9338816687809</v>
       </c>
       <c r="D71">
-        <v>344.1442503371873</v>
+        <v>345.0738816687809</v>
       </c>
       <c r="E71">
-        <v>200.238</v>
+        <v>203.14</v>
       </c>
       <c r="F71">
-        <v>200.238</v>
+        <v>203.14</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -7109,28 +7109,28 @@
         <v>62.2</v>
       </c>
       <c r="M71">
-        <v>11.0731614</v>
+        <v>11.233642</v>
       </c>
       <c r="N71">
-        <v>51.1268386</v>
+        <v>50.966358</v>
       </c>
       <c r="O71">
-        <v>15.33805158</v>
+        <v>15.2899074</v>
       </c>
       <c r="P71">
-        <v>35.78878702</v>
+        <v>35.6764506</v>
       </c>
       <c r="Q71">
-        <v>41.28878702</v>
+        <v>41.1764506</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2502551199462815</v>
+        <v>0.2562710335218342</v>
       </c>
       <c r="T71">
-        <v>1.425551578869624</v>
+        <v>1.467497190690084</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>5.617185350517874</v>
+        <v>5.536939845510476</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1039783100565502</v>
+        <v>0.1036676329297532</v>
       </c>
       <c r="C72">
-        <v>141.9338816687809</v>
+        <v>139.9665490003864</v>
       </c>
       <c r="D72">
-        <v>345.0738816687809</v>
+        <v>346.0085490003864</v>
       </c>
       <c r="E72">
-        <v>203.14</v>
+        <v>206.042</v>
       </c>
       <c r="F72">
-        <v>203.14</v>
+        <v>206.042</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -7191,28 +7191,28 @@
         <v>62.2</v>
       </c>
       <c r="M72">
-        <v>11.233642</v>
+        <v>11.3941226</v>
       </c>
       <c r="N72">
-        <v>50.966358</v>
+        <v>50.8058774</v>
       </c>
       <c r="O72">
-        <v>15.2899074</v>
+        <v>15.24176322</v>
       </c>
       <c r="P72">
-        <v>35.6764506</v>
+        <v>35.56411418</v>
       </c>
       <c r="Q72">
-        <v>41.1764506</v>
+        <v>41.06411418</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2562710335218342</v>
+        <v>0.2627018376888042</v>
       </c>
       <c r="T72">
-        <v>1.467497190690084</v>
+        <v>1.512335603325748</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>5.536939845510476</v>
+        <v>5.45895477726385</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1036676329297532</v>
+        <v>0.1033569558029562</v>
       </c>
       <c r="C73">
-        <v>139.9665490003864</v>
+        <v>138.0042933646832</v>
       </c>
       <c r="D73">
-        <v>346.0085490003864</v>
+        <v>346.9482933646832</v>
       </c>
       <c r="E73">
-        <v>206.042</v>
+        <v>208.944</v>
       </c>
       <c r="F73">
-        <v>206.042</v>
+        <v>208.944</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -7273,28 +7273,28 @@
         <v>62.2</v>
       </c>
       <c r="M73">
-        <v>11.3941226</v>
+        <v>11.5546032</v>
       </c>
       <c r="N73">
-        <v>50.8058774</v>
+        <v>50.6453968</v>
       </c>
       <c r="O73">
-        <v>15.24176322</v>
+        <v>15.19361904</v>
       </c>
       <c r="P73">
-        <v>35.56411418</v>
+        <v>35.45177776</v>
       </c>
       <c r="Q73">
-        <v>41.06411418</v>
+        <v>40.95177776</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2627018376888042</v>
+        <v>0.2695919850105578</v>
       </c>
       <c r="T73">
-        <v>1.512335603325748</v>
+        <v>1.560376759721102</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>5.45895477726385</v>
+        <v>5.383135960912964</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1033569558029562</v>
+        <v>0.1030462786761592</v>
       </c>
       <c r="C74">
-        <v>138.0042933646832</v>
+        <v>136.0471562413367</v>
       </c>
       <c r="D74">
-        <v>346.9482933646832</v>
+        <v>347.8931562413367</v>
       </c>
       <c r="E74">
-        <v>208.944</v>
+        <v>211.846</v>
       </c>
       <c r="F74">
-        <v>208.944</v>
+        <v>211.846</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -7355,28 +7355,28 @@
         <v>62.2</v>
       </c>
       <c r="M74">
-        <v>11.5546032</v>
+        <v>11.7150838</v>
       </c>
       <c r="N74">
-        <v>50.6453968</v>
+        <v>50.4849162</v>
       </c>
       <c r="O74">
-        <v>15.19361904</v>
+        <v>15.14547486</v>
       </c>
       <c r="P74">
-        <v>35.45177776</v>
+        <v>35.33944134</v>
       </c>
       <c r="Q74">
-        <v>40.95177776</v>
+        <v>40.83944134</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2695919850105578</v>
+        <v>0.2769925136154043</v>
       </c>
       <c r="T74">
-        <v>1.560376759721102</v>
+        <v>1.611976520293889</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>5.383135960912964</v>
+        <v>5.309394372407307</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1030462786761592</v>
+        <v>0.1027356015493621</v>
       </c>
       <c r="C75">
-        <v>136.0471562413367</v>
+        <v>134.0951795631015</v>
       </c>
       <c r="D75">
-        <v>347.8931562413367</v>
+        <v>348.8431795631014</v>
       </c>
       <c r="E75">
-        <v>211.846</v>
+        <v>214.748</v>
       </c>
       <c r="F75">
-        <v>211.846</v>
+        <v>214.748</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -7437,28 +7437,28 @@
         <v>62.2</v>
       </c>
       <c r="M75">
-        <v>11.7150838</v>
+        <v>11.8755644</v>
       </c>
       <c r="N75">
-        <v>50.4849162</v>
+        <v>50.3244356</v>
       </c>
       <c r="O75">
-        <v>15.14547486</v>
+        <v>15.09733068</v>
       </c>
       <c r="P75">
-        <v>35.33944134</v>
+        <v>35.22710492</v>
       </c>
       <c r="Q75">
-        <v>40.83944134</v>
+        <v>40.72710492</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2769925136154043</v>
+        <v>0.2849623136513928</v>
       </c>
       <c r="T75">
-        <v>1.611976520293889</v>
+        <v>1.66754549321843</v>
       </c>
       <c r="U75">
         <v>0.0553</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>5.309394372407307</v>
+        <v>5.237645799807208</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1027356015493621</v>
+        <v>0.1024249244225651</v>
       </c>
       <c r="C76">
-        <v>134.0951795631015</v>
+        <v>132.1484057220247</v>
       </c>
       <c r="D76">
-        <v>348.8431795631014</v>
+        <v>349.7984057220247</v>
       </c>
       <c r="E76">
-        <v>214.748</v>
+        <v>217.65</v>
       </c>
       <c r="F76">
-        <v>214.748</v>
+        <v>217.65</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -7519,28 +7519,28 @@
         <v>62.2</v>
       </c>
       <c r="M76">
-        <v>11.8755644</v>
+        <v>12.036045</v>
       </c>
       <c r="N76">
-        <v>50.3244356</v>
+        <v>50.163955</v>
       </c>
       <c r="O76">
-        <v>15.09733068</v>
+        <v>15.0491865</v>
       </c>
       <c r="P76">
-        <v>35.22710492</v>
+        <v>35.1147685</v>
       </c>
       <c r="Q76">
-        <v>40.72710492</v>
+        <v>40.6147685</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2849623136513928</v>
+        <v>0.2935696976902604</v>
       </c>
       <c r="T76">
-        <v>1.66754549321843</v>
+        <v>1.727559983976934</v>
       </c>
       <c r="U76">
         <v>0.0553</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>5.237645799807208</v>
+        <v>5.167810522476445</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1024249244225651</v>
+        <v>0.1021142472957681</v>
       </c>
       <c r="C77">
-        <v>132.1484057220247</v>
+        <v>130.2068775757513</v>
       </c>
       <c r="D77">
-        <v>349.7984057220247</v>
+        <v>350.7588775757513</v>
       </c>
       <c r="E77">
-        <v>217.65</v>
+        <v>220.552</v>
       </c>
       <c r="F77">
-        <v>217.65</v>
+        <v>220.552</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -7601,28 +7601,28 @@
         <v>62.2</v>
       </c>
       <c r="M77">
-        <v>12.036045</v>
+        <v>12.1965256</v>
       </c>
       <c r="N77">
-        <v>50.163955</v>
+        <v>50.0034744</v>
       </c>
       <c r="O77">
-        <v>15.0491865</v>
+        <v>15.00104232</v>
       </c>
       <c r="P77">
-        <v>35.1147685</v>
+        <v>35.00243208000001</v>
       </c>
       <c r="Q77">
-        <v>40.6147685</v>
+        <v>40.50243208000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2935696976902604</v>
+        <v>0.302894363732367</v>
       </c>
       <c r="T77">
-        <v>1.727559983976934</v>
+        <v>1.792575682298647</v>
       </c>
       <c r="U77">
         <v>0.0553</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>5.167810522476445</v>
+        <v>5.099813015601755</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1021142472957681</v>
+        <v>0.1018035701689711</v>
       </c>
       <c r="C78">
-        <v>130.2068775757513</v>
+        <v>128.2706384539346</v>
       </c>
       <c r="D78">
-        <v>350.7588775757513</v>
+        <v>351.7246384539346</v>
       </c>
       <c r="E78">
-        <v>220.552</v>
+        <v>223.454</v>
       </c>
       <c r="F78">
-        <v>220.552</v>
+        <v>223.454</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -7683,28 +7683,28 @@
         <v>62.2</v>
       </c>
       <c r="M78">
-        <v>12.1965256</v>
+        <v>12.3570062</v>
       </c>
       <c r="N78">
-        <v>50.0034744</v>
+        <v>49.8429938</v>
       </c>
       <c r="O78">
-        <v>15.00104232</v>
+        <v>14.95289814</v>
       </c>
       <c r="P78">
-        <v>35.00243208000001</v>
+        <v>34.89009566</v>
       </c>
       <c r="Q78">
-        <v>40.50243208000001</v>
+        <v>40.39009566</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.302894363732367</v>
+        <v>0.3130298702998742</v>
       </c>
       <c r="T78">
-        <v>1.792575682298647</v>
+        <v>1.863244919604856</v>
       </c>
       <c r="U78">
         <v>0.0553</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>5.099813015601755</v>
+        <v>5.033581677736796</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1018035701689711</v>
+        <v>0.101492893042174</v>
       </c>
       <c r="C79">
-        <v>128.2706384539346</v>
+        <v>126.3397321647512</v>
       </c>
       <c r="D79">
-        <v>351.7246384539346</v>
+        <v>352.6957321647512</v>
       </c>
       <c r="E79">
-        <v>223.454</v>
+        <v>226.356</v>
       </c>
       <c r="F79">
-        <v>223.454</v>
+        <v>226.356</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -7765,28 +7765,28 @@
         <v>62.2</v>
       </c>
       <c r="M79">
-        <v>12.3570062</v>
+        <v>12.5174868</v>
       </c>
       <c r="N79">
-        <v>49.8429938</v>
+        <v>49.6825132</v>
       </c>
       <c r="O79">
-        <v>14.95289814</v>
+        <v>14.90475396</v>
       </c>
       <c r="P79">
-        <v>34.89009566</v>
+        <v>34.77775924</v>
       </c>
       <c r="Q79">
-        <v>40.39009566</v>
+        <v>40.27775924</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3130298702998742</v>
+        <v>0.3240867865553365</v>
       </c>
       <c r="T79">
-        <v>1.863244919604856</v>
+        <v>1.940338633029812</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>5.033581677736796</v>
+        <v>4.969048579304274</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.101492893042174</v>
+        <v>0.101182215915377</v>
       </c>
       <c r="C80">
-        <v>126.3397321647512</v>
+        <v>124.4142030015261</v>
       </c>
       <c r="D80">
-        <v>352.6957321647512</v>
+        <v>353.6722030015262</v>
       </c>
       <c r="E80">
-        <v>226.356</v>
+        <v>229.258</v>
       </c>
       <c r="F80">
-        <v>226.356</v>
+        <v>229.258</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -7847,28 +7847,28 @@
         <v>62.2</v>
       </c>
       <c r="M80">
-        <v>12.5174868</v>
+        <v>12.6779674</v>
       </c>
       <c r="N80">
-        <v>49.6825132</v>
+        <v>49.5220326</v>
       </c>
       <c r="O80">
-        <v>14.90475396</v>
+        <v>14.85660978</v>
       </c>
       <c r="P80">
-        <v>34.77775924</v>
+        <v>34.66542282</v>
       </c>
       <c r="Q80">
-        <v>40.27775924</v>
+        <v>40.16542282</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3240867865553365</v>
+        <v>0.3361967424541762</v>
       </c>
       <c r="T80">
-        <v>1.940338633029812</v>
+        <v>2.024774604876192</v>
       </c>
       <c r="U80">
         <v>0.0553</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>4.969048579304274</v>
+        <v>4.906149230199156</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.101182215915377</v>
+        <v>0.10087153878858</v>
       </c>
       <c r="C81">
-        <v>124.4142030015261</v>
+        <v>122.4940957494665</v>
       </c>
       <c r="D81">
-        <v>353.6722030015262</v>
+        <v>354.6540957494665</v>
       </c>
       <c r="E81">
-        <v>229.258</v>
+        <v>232.16</v>
       </c>
       <c r="F81">
-        <v>229.258</v>
+        <v>232.16</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -7929,28 +7929,28 @@
         <v>62.2</v>
       </c>
       <c r="M81">
-        <v>12.6779674</v>
+        <v>12.838448</v>
       </c>
       <c r="N81">
-        <v>49.5220326</v>
+        <v>49.361552</v>
       </c>
       <c r="O81">
-        <v>14.85660978</v>
+        <v>14.8084656</v>
       </c>
       <c r="P81">
-        <v>34.66542282</v>
+        <v>34.55308640000001</v>
       </c>
       <c r="Q81">
-        <v>40.16542282</v>
+        <v>40.05308640000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3361967424541762</v>
+        <v>0.3495176939428999</v>
       </c>
       <c r="T81">
-        <v>2.024774604876192</v>
+        <v>2.117654173907209</v>
       </c>
       <c r="U81">
         <v>0.0553</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>4.906149230199156</v>
+        <v>4.844822364821667</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.10087153878858</v>
+        <v>0.1005608616617829</v>
       </c>
       <c r="C82">
-        <v>122.4940957494665</v>
+        <v>120.5794556925095</v>
       </c>
       <c r="D82">
-        <v>354.6540957494665</v>
+        <v>355.6414556925095</v>
       </c>
       <c r="E82">
-        <v>232.16</v>
+        <v>235.062</v>
       </c>
       <c r="F82">
-        <v>232.16</v>
+        <v>235.062</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -8011,28 +8011,28 @@
         <v>62.2</v>
       </c>
       <c r="M82">
-        <v>12.838448</v>
+        <v>12.9989286</v>
       </c>
       <c r="N82">
-        <v>49.361552</v>
+        <v>49.2010714</v>
       </c>
       <c r="O82">
-        <v>14.8084656</v>
+        <v>14.76032142</v>
       </c>
       <c r="P82">
-        <v>34.55308640000001</v>
+        <v>34.44074998000001</v>
       </c>
       <c r="Q82">
-        <v>40.05308640000001</v>
+        <v>39.94074998000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3495176939428999</v>
+        <v>0.3642408508514893</v>
       </c>
       <c r="T82">
-        <v>2.117654173907209</v>
+        <v>2.220310539678335</v>
       </c>
       <c r="U82">
         <v>0.0553</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>4.844822364821667</v>
+        <v>4.785009743033745</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1005608616617829</v>
+        <v>0.1002501845349859</v>
       </c>
       <c r="C83">
-        <v>120.5794556925095</v>
+        <v>118.6703286202831</v>
       </c>
       <c r="D83">
-        <v>355.6414556925095</v>
+        <v>356.6343286202831</v>
       </c>
       <c r="E83">
-        <v>235.062</v>
+        <v>237.964</v>
       </c>
       <c r="F83">
-        <v>235.062</v>
+        <v>237.964</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -8093,28 +8093,28 @@
         <v>62.2</v>
       </c>
       <c r="M83">
-        <v>12.9989286</v>
+        <v>13.1594092</v>
       </c>
       <c r="N83">
-        <v>49.2010714</v>
+        <v>49.0405908</v>
       </c>
       <c r="O83">
-        <v>14.76032142</v>
+        <v>14.71217724</v>
       </c>
       <c r="P83">
-        <v>34.44074998000001</v>
+        <v>34.32841356</v>
       </c>
       <c r="Q83">
-        <v>39.94074998000001</v>
+        <v>39.82841356</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3642408508514893</v>
+        <v>0.3805999140832552</v>
       </c>
       <c r="T83">
-        <v>2.220310539678335</v>
+        <v>2.334373168312919</v>
       </c>
       <c r="U83">
         <v>0.0553</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>4.785009743033745</v>
+        <v>4.726655965679675</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1002501845349859</v>
+        <v>0.09993950740818888</v>
       </c>
       <c r="C84">
-        <v>118.6703286202831</v>
+        <v>116.7667608351855</v>
       </c>
       <c r="D84">
-        <v>356.6343286202831</v>
+        <v>357.6327608351855</v>
       </c>
       <c r="E84">
-        <v>237.964</v>
+        <v>240.866</v>
       </c>
       <c r="F84">
-        <v>237.964</v>
+        <v>240.866</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -8175,28 +8175,28 @@
         <v>62.2</v>
       </c>
       <c r="M84">
-        <v>13.1594092</v>
+        <v>13.3198898</v>
       </c>
       <c r="N84">
-        <v>49.0405908</v>
+        <v>48.8801102</v>
       </c>
       <c r="O84">
-        <v>14.71217724</v>
+        <v>14.66403306</v>
       </c>
       <c r="P84">
-        <v>34.32841356</v>
+        <v>34.21607714</v>
       </c>
       <c r="Q84">
-        <v>39.82841356</v>
+        <v>39.71607714</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3805999140832552</v>
+        <v>0.3988835729893466</v>
       </c>
       <c r="T84">
-        <v>2.334373168312919</v>
+        <v>2.461854929728041</v>
       </c>
       <c r="U84">
         <v>0.0553</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>4.726655965679675</v>
+        <v>4.669708303442571</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09993950740818888</v>
+        <v>0.09962883028139187</v>
       </c>
       <c r="C85">
-        <v>116.7667608351855</v>
+        <v>114.8687991595826</v>
       </c>
       <c r="D85">
-        <v>357.6327608351855</v>
+        <v>358.6367991595826</v>
       </c>
       <c r="E85">
-        <v>240.866</v>
+        <v>243.768</v>
       </c>
       <c r="F85">
-        <v>240.866</v>
+        <v>243.768</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -8257,28 +8257,28 @@
         <v>62.2</v>
       </c>
       <c r="M85">
-        <v>13.3198898</v>
+        <v>13.4803704</v>
       </c>
       <c r="N85">
-        <v>48.8801102</v>
+        <v>48.7196296</v>
       </c>
       <c r="O85">
-        <v>14.66403306</v>
+        <v>14.61588888</v>
       </c>
       <c r="P85">
-        <v>34.21607714</v>
+        <v>34.10374072</v>
       </c>
       <c r="Q85">
-        <v>39.71607714</v>
+        <v>39.60374072</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3988835729893466</v>
+        <v>0.4194526892586994</v>
       </c>
       <c r="T85">
-        <v>2.461854929728041</v>
+        <v>2.605271911320055</v>
       </c>
       <c r="U85">
         <v>0.0553</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>4.669708303442571</v>
+        <v>4.614116537925398</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09962883028139187</v>
+        <v>0.09931815315459486</v>
       </c>
       <c r="C86">
-        <v>114.8687991595826</v>
+        <v>112.9764909431277</v>
       </c>
       <c r="D86">
-        <v>358.6367991595826</v>
+        <v>359.6464909431277</v>
       </c>
       <c r="E86">
-        <v>243.768</v>
+        <v>246.67</v>
       </c>
       <c r="F86">
-        <v>243.768</v>
+        <v>246.67</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -8339,28 +8339,28 @@
         <v>62.2</v>
       </c>
       <c r="M86">
-        <v>13.4803704</v>
+        <v>13.640851</v>
       </c>
       <c r="N86">
-        <v>48.7196296</v>
+        <v>48.55914900000001</v>
       </c>
       <c r="O86">
-        <v>14.61588888</v>
+        <v>14.5677447</v>
       </c>
       <c r="P86">
-        <v>34.10374072</v>
+        <v>33.99140430000001</v>
       </c>
       <c r="Q86">
-        <v>39.60374072</v>
+        <v>39.49140430000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4194526892586991</v>
+        <v>0.4427643543639656</v>
       </c>
       <c r="T86">
-        <v>2.605271911320053</v>
+        <v>2.767811157124335</v>
       </c>
       <c r="U86">
         <v>0.0553</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>4.614116537925398</v>
+        <v>4.559832813949805</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09931815315459486</v>
+        <v>0.09900747602779782</v>
       </c>
       <c r="C87">
-        <v>112.9764909431277</v>
+        <v>111.089884070205</v>
       </c>
       <c r="D87">
-        <v>359.6464909431277</v>
+        <v>360.661884070205</v>
       </c>
       <c r="E87">
-        <v>246.67</v>
+        <v>249.572</v>
       </c>
       <c r="F87">
-        <v>246.67</v>
+        <v>249.572</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -8421,28 +8421,28 @@
         <v>62.2</v>
       </c>
       <c r="M87">
-        <v>13.640851</v>
+        <v>13.8013316</v>
       </c>
       <c r="N87">
-        <v>48.55914900000001</v>
+        <v>48.39866840000001</v>
       </c>
       <c r="O87">
-        <v>14.5677447</v>
+        <v>14.51960052</v>
       </c>
       <c r="P87">
-        <v>33.99140430000001</v>
+        <v>33.87906788000001</v>
       </c>
       <c r="Q87">
-        <v>39.49140430000001</v>
+        <v>39.37906788000001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4427643543639656</v>
+        <v>0.4694062573414129</v>
       </c>
       <c r="T87">
-        <v>2.767811157124335</v>
+        <v>2.95357029518637</v>
       </c>
       <c r="U87">
         <v>0.0553</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>4.559832813949805</v>
+        <v>4.506811502159691</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09900747602779782</v>
+        <v>0.1002192989010008</v>
       </c>
       <c r="C88">
-        <v>111.089884070205</v>
+        <v>104.2593370623529</v>
       </c>
       <c r="D88">
-        <v>360.661884070205</v>
+        <v>356.7333370623529</v>
       </c>
       <c r="E88">
-        <v>249.572</v>
+        <v>252.474</v>
       </c>
       <c r="F88">
-        <v>249.572</v>
+        <v>252.474</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -8503,45 +8503,45 @@
         <v>62.2</v>
       </c>
       <c r="M88">
-        <v>13.8013316</v>
+        <v>14.5929972</v>
       </c>
       <c r="N88">
-        <v>48.39866840000001</v>
+        <v>47.6070028</v>
       </c>
       <c r="O88">
-        <v>14.51960052</v>
+        <v>14.28210084</v>
       </c>
       <c r="P88">
-        <v>33.87906788000001</v>
+        <v>33.32490196000001</v>
       </c>
       <c r="Q88">
-        <v>39.37906788000001</v>
+        <v>38.82490196000001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4694062573414129</v>
+        <v>0.5001469146230829</v>
       </c>
       <c r="T88">
-        <v>2.95357029518637</v>
+        <v>3.167907762181028</v>
       </c>
       <c r="U88">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V88">
         <v>0.3</v>
       </c>
       <c r="W88">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y88">
-        <v>4.506811502159691</v>
+        <v>4.262318367333066</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1002192989010008</v>
+        <v>0.09992612177420378</v>
       </c>
       <c r="C89">
-        <v>104.2593370623529</v>
+        <v>102.2999042771294</v>
       </c>
       <c r="D89">
-        <v>356.7333370623529</v>
+        <v>357.6759042771294</v>
       </c>
       <c r="E89">
-        <v>252.474</v>
+        <v>255.376</v>
       </c>
       <c r="F89">
-        <v>252.474</v>
+        <v>255.376</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -8585,28 +8585,28 @@
         <v>62.2</v>
       </c>
       <c r="M89">
-        <v>14.5929972</v>
+        <v>14.7607328</v>
       </c>
       <c r="N89">
-        <v>47.6070028</v>
+        <v>47.4392672</v>
       </c>
       <c r="O89">
-        <v>14.28210084</v>
+        <v>14.23178016</v>
       </c>
       <c r="P89">
-        <v>33.32490196000001</v>
+        <v>33.20748704</v>
       </c>
       <c r="Q89">
-        <v>38.82490196000001</v>
+        <v>38.70748704</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5001469146230829</v>
+        <v>0.5360110147850314</v>
       </c>
       <c r="T89">
-        <v>3.167907762181028</v>
+        <v>3.417968140341461</v>
       </c>
       <c r="U89">
         <v>0.0578</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>4.262318367333066</v>
+        <v>4.213882931340645</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.09992612177420378</v>
+        <v>0.09963294464740674</v>
       </c>
       <c r="C90">
-        <v>102.2999042771294</v>
+        <v>100.3454656234557</v>
       </c>
       <c r="D90">
-        <v>357.6759042771294</v>
+        <v>358.6234656234557</v>
       </c>
       <c r="E90">
-        <v>255.376</v>
+        <v>258.278</v>
       </c>
       <c r="F90">
-        <v>255.376</v>
+        <v>258.278</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -8667,28 +8667,28 @@
         <v>62.2</v>
       </c>
       <c r="M90">
-        <v>14.7607328</v>
+        <v>14.9284684</v>
       </c>
       <c r="N90">
-        <v>47.4392672</v>
+        <v>47.2715316</v>
       </c>
       <c r="O90">
-        <v>14.23178016</v>
+        <v>14.18145948</v>
       </c>
       <c r="P90">
-        <v>33.20748704</v>
+        <v>33.09007212</v>
       </c>
       <c r="Q90">
-        <v>38.70748704</v>
+        <v>38.59007212</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5360110147850314</v>
+        <v>0.5783958604309704</v>
       </c>
       <c r="T90">
-        <v>3.417968140341461</v>
+        <v>3.713494041803791</v>
       </c>
       <c r="U90">
         <v>0.0578</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>4.213882931340645</v>
+        <v>4.166535932112097</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.09963294464740674</v>
+        <v>0.0993397675206097</v>
       </c>
       <c r="C91">
-        <v>100.3454656234557</v>
+        <v>98.3960608983881</v>
       </c>
       <c r="D91">
-        <v>358.6234656234557</v>
+        <v>359.5760608983881</v>
       </c>
       <c r="E91">
-        <v>258.278</v>
+        <v>261.18</v>
       </c>
       <c r="F91">
-        <v>258.278</v>
+        <v>261.18</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -8749,28 +8749,28 @@
         <v>62.2</v>
       </c>
       <c r="M91">
-        <v>14.9284684</v>
+        <v>15.096204</v>
       </c>
       <c r="N91">
-        <v>47.2715316</v>
+        <v>47.103796</v>
       </c>
       <c r="O91">
-        <v>14.18145948</v>
+        <v>14.1311388</v>
       </c>
       <c r="P91">
-        <v>33.09007212</v>
+        <v>32.9726572</v>
       </c>
       <c r="Q91">
-        <v>38.59007212</v>
+        <v>38.4726572</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5783958604309704</v>
+        <v>0.6292576752060971</v>
       </c>
       <c r="T91">
-        <v>3.713494041803791</v>
+        <v>4.068125123558587</v>
       </c>
       <c r="U91">
         <v>0.0578</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>4.166535932112097</v>
+        <v>4.120241088421963</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.0993397675206097</v>
+        <v>0.09904659039381269</v>
       </c>
       <c r="C92">
-        <v>98.3960608983881</v>
+        <v>96.45173032295378</v>
       </c>
       <c r="D92">
-        <v>359.5760608983881</v>
+        <v>360.5337303229538</v>
       </c>
       <c r="E92">
-        <v>261.18</v>
+        <v>264.082</v>
       </c>
       <c r="F92">
-        <v>261.18</v>
+        <v>264.082</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -8831,28 +8831,28 @@
         <v>62.2</v>
       </c>
       <c r="M92">
-        <v>15.096204</v>
+        <v>15.2639396</v>
       </c>
       <c r="N92">
-        <v>47.103796</v>
+        <v>46.9360604</v>
       </c>
       <c r="O92">
-        <v>14.1311388</v>
+        <v>14.08081812</v>
       </c>
       <c r="P92">
-        <v>32.9726572</v>
+        <v>32.85524228</v>
       </c>
       <c r="Q92">
-        <v>38.4726572</v>
+        <v>38.35524228</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6292576752060971</v>
+        <v>0.6914221154868078</v>
       </c>
       <c r="T92">
-        <v>4.068125123558587</v>
+        <v>4.501563112370005</v>
       </c>
       <c r="U92">
         <v>0.0578</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>4.120241088421963</v>
+        <v>4.074963713823919</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.09904659039381269</v>
+        <v>0.09875341326701567</v>
       </c>
       <c r="C93">
-        <v>96.45173032295378</v>
+        <v>94.51251454781175</v>
       </c>
       <c r="D93">
-        <v>360.5337303229538</v>
+        <v>361.4965145478117</v>
       </c>
       <c r="E93">
-        <v>264.082</v>
+        <v>266.984</v>
       </c>
       <c r="F93">
-        <v>264.082</v>
+        <v>266.984</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -8913,28 +8913,28 @@
         <v>62.2</v>
       </c>
       <c r="M93">
-        <v>15.2639396</v>
+        <v>15.4316752</v>
       </c>
       <c r="N93">
-        <v>46.9360604</v>
+        <v>46.7683248</v>
       </c>
       <c r="O93">
-        <v>14.08081812</v>
+        <v>14.03049744</v>
       </c>
       <c r="P93">
-        <v>32.85524228</v>
+        <v>32.73782736</v>
       </c>
       <c r="Q93">
-        <v>38.35524228</v>
+        <v>38.23782736</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6914221154868078</v>
+        <v>0.7691276658376961</v>
       </c>
       <c r="T93">
-        <v>4.501563112370005</v>
+        <v>5.043360598384278</v>
       </c>
       <c r="U93">
         <v>0.0578</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>4.074963713823919</v>
+        <v>4.030670629978008</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.09875341326701567</v>
+        <v>0.1007387361402186</v>
       </c>
       <c r="C94">
-        <v>94.51251454781175</v>
+        <v>85.18948287915305</v>
       </c>
       <c r="D94">
-        <v>361.4965145478117</v>
+        <v>355.0754828791531</v>
       </c>
       <c r="E94">
-        <v>266.984</v>
+        <v>269.886</v>
       </c>
       <c r="F94">
-        <v>266.984</v>
+        <v>269.886</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -8995,45 +8995,45 @@
         <v>62.2</v>
       </c>
       <c r="M94">
-        <v>15.4316752</v>
+        <v>16.5440118</v>
       </c>
       <c r="N94">
-        <v>46.7683248</v>
+        <v>45.6559882</v>
       </c>
       <c r="O94">
-        <v>14.03049744</v>
+        <v>13.69679646</v>
       </c>
       <c r="P94">
-        <v>32.73782736</v>
+        <v>31.95919174</v>
       </c>
       <c r="Q94">
-        <v>38.23782736</v>
+        <v>37.45919174</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7691276658376961</v>
+        <v>0.8690348020031238</v>
       </c>
       <c r="T94">
-        <v>5.043360598384278</v>
+        <v>5.739957366116913</v>
       </c>
       <c r="U94">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V94">
         <v>0.3</v>
       </c>
       <c r="W94">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y94">
-        <v>4.030670629978008</v>
+        <v>3.759668498302208</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1007387361402186</v>
+        <v>0.1004700590134216</v>
       </c>
       <c r="C95">
-        <v>85.18948287915305</v>
+        <v>83.14307376873023</v>
       </c>
       <c r="D95">
-        <v>355.0754828791531</v>
+        <v>355.9310737687302</v>
       </c>
       <c r="E95">
-        <v>269.886</v>
+        <v>272.788</v>
       </c>
       <c r="F95">
-        <v>269.886</v>
+        <v>272.788</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -9077,28 +9077,28 @@
         <v>62.2</v>
       </c>
       <c r="M95">
-        <v>16.5440118</v>
+        <v>16.7219044</v>
       </c>
       <c r="N95">
-        <v>45.6559882</v>
+        <v>45.4780956</v>
       </c>
       <c r="O95">
-        <v>13.69679646</v>
+        <v>13.64342868</v>
       </c>
       <c r="P95">
-        <v>31.95919174</v>
+        <v>31.83466692</v>
       </c>
       <c r="Q95">
-        <v>37.45919174</v>
+        <v>37.33466692</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8690348020031238</v>
+        <v>1.002244316890361</v>
       </c>
       <c r="T95">
-        <v>5.739957366116913</v>
+        <v>6.668753056427096</v>
       </c>
       <c r="U95">
         <v>0.0613</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>3.759668498302208</v>
+        <v>3.719672024916014</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1004700590134216</v>
+        <v>0.1002013818866246</v>
       </c>
       <c r="C96">
-        <v>83.14307376873023</v>
+        <v>81.10079788620828</v>
       </c>
       <c r="D96">
-        <v>355.9310737687302</v>
+        <v>356.7907978862083</v>
       </c>
       <c r="E96">
-        <v>272.788</v>
+        <v>275.69</v>
       </c>
       <c r="F96">
-        <v>272.788</v>
+        <v>275.69</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -9159,28 +9159,28 @@
         <v>62.2</v>
       </c>
       <c r="M96">
-        <v>16.7219044</v>
+        <v>16.899797</v>
       </c>
       <c r="N96">
-        <v>45.4780956</v>
+        <v>45.300203</v>
       </c>
       <c r="O96">
-        <v>13.64342868</v>
+        <v>13.5900609</v>
       </c>
       <c r="P96">
-        <v>31.83466692</v>
+        <v>31.7101421</v>
       </c>
       <c r="Q96">
-        <v>37.33466692</v>
+        <v>37.2101421</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.002244316890361</v>
+        <v>1.188737637732493</v>
       </c>
       <c r="T96">
-        <v>6.668753056427096</v>
+        <v>7.969067022861351</v>
       </c>
       <c r="U96">
         <v>0.0613</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>3.719672024916014</v>
+        <v>3.680517582548477</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1002013818866246</v>
+        <v>0.09993270475982755</v>
       </c>
       <c r="C97">
-        <v>81.10079788620828</v>
+        <v>79.06268525458751</v>
       </c>
       <c r="D97">
-        <v>356.7907978862083</v>
+        <v>357.6546852545875</v>
       </c>
       <c r="E97">
-        <v>275.69</v>
+        <v>278.592</v>
       </c>
       <c r="F97">
-        <v>275.69</v>
+        <v>278.592</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -9241,28 +9241,28 @@
         <v>62.2</v>
       </c>
       <c r="M97">
-        <v>16.899797</v>
+        <v>17.0776896</v>
       </c>
       <c r="N97">
-        <v>45.300203</v>
+        <v>45.1223104</v>
       </c>
       <c r="O97">
-        <v>13.5900609</v>
+        <v>13.53669312</v>
       </c>
       <c r="P97">
-        <v>31.7101421</v>
+        <v>31.58561728</v>
       </c>
       <c r="Q97">
-        <v>37.2101421</v>
+        <v>37.08561728</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.188737637732493</v>
+        <v>1.468477618995692</v>
       </c>
       <c r="T97">
-        <v>7.969067022861351</v>
+        <v>9.919537972512737</v>
       </c>
       <c r="U97">
         <v>0.0613</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>3.680517582548477</v>
+        <v>3.642178857730264</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.09993270475982755</v>
+        <v>0.09966402763303053</v>
       </c>
       <c r="C98">
-        <v>79.06268525458751</v>
+        <v>77.02876618834864</v>
       </c>
       <c r="D98">
-        <v>357.6546852545875</v>
+        <v>358.5227661883486</v>
       </c>
       <c r="E98">
-        <v>278.592</v>
+        <v>281.494</v>
       </c>
       <c r="F98">
-        <v>278.592</v>
+        <v>281.494</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -9323,28 +9323,28 @@
         <v>62.2</v>
       </c>
       <c r="M98">
-        <v>17.0776896</v>
+        <v>17.2555822</v>
       </c>
       <c r="N98">
-        <v>45.1223104</v>
+        <v>44.9444178</v>
       </c>
       <c r="O98">
-        <v>13.53669312</v>
+        <v>13.48332534</v>
       </c>
       <c r="P98">
-        <v>31.58561728</v>
+        <v>31.46109246</v>
       </c>
       <c r="Q98">
-        <v>37.08561728</v>
+        <v>36.96109246</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.468477618995688</v>
+        <v>1.934710921101016</v>
       </c>
       <c r="T98">
-        <v>9.919537972512709</v>
+        <v>13.17032288859834</v>
       </c>
       <c r="U98">
         <v>0.0613</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>3.642178857730264</v>
+        <v>3.60463062208356</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.09966402763303053</v>
+        <v>0.09939535050623349</v>
       </c>
       <c r="C99">
-        <v>77.02876618834864</v>
+        <v>74.999071297</v>
       </c>
       <c r="D99">
-        <v>358.5227661883486</v>
+        <v>359.395071297</v>
       </c>
       <c r="E99">
-        <v>281.494</v>
+        <v>284.396</v>
       </c>
       <c r="F99">
-        <v>281.494</v>
+        <v>284.396</v>
       </c>
       <c r="G99">
         <v>0</v>
@@ -9405,28 +9405,28 @@
         <v>62.2</v>
       </c>
       <c r="M99">
-        <v>17.2555822</v>
+        <v>17.4334748</v>
       </c>
       <c r="N99">
-        <v>44.9444178</v>
+        <v>44.7665252</v>
       </c>
       <c r="O99">
-        <v>13.48332534</v>
+        <v>13.42995756</v>
       </c>
       <c r="P99">
-        <v>31.46109246</v>
+        <v>31.33656764000001</v>
       </c>
       <c r="Q99">
-        <v>36.96109246</v>
+        <v>36.83656764000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.934710921101016</v>
+        <v>2.867177525311673</v>
       </c>
       <c r="T99">
-        <v>13.17032288859834</v>
+        <v>19.67189272076959</v>
       </c>
       <c r="U99">
         <v>0.0613</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>3.60463062208356</v>
+        <v>3.567848676960259</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.09939535050623349</v>
+        <v>0.09912667337943648</v>
       </c>
       <c r="C100">
-        <v>74.999071297</v>
+        <v>72.97363148867436</v>
       </c>
       <c r="D100">
-        <v>359.395071297</v>
+        <v>360.2716314886744</v>
       </c>
       <c r="E100">
-        <v>284.396</v>
+        <v>287.298</v>
       </c>
       <c r="F100">
-        <v>284.396</v>
+        <v>287.298</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -9487,28 +9487,28 @@
         <v>62.2</v>
       </c>
       <c r="M100">
-        <v>17.4334748</v>
+        <v>17.6113674</v>
       </c>
       <c r="N100">
-        <v>44.7665252</v>
+        <v>44.5886326</v>
       </c>
       <c r="O100">
-        <v>13.42995756</v>
+        <v>13.37658978</v>
       </c>
       <c r="P100">
-        <v>31.33656764000001</v>
+        <v>31.21204282</v>
       </c>
       <c r="Q100">
-        <v>36.83656764000001</v>
+        <v>36.71204282</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.867177525311673</v>
+        <v>5.664577337943643</v>
       </c>
       <c r="T100">
-        <v>19.67189272076959</v>
+        <v>39.17660221728335</v>
       </c>
       <c r="U100">
         <v>0.0613</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>3.567848676960259</v>
+        <v>3.531809801435407</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.09912667337943648</v>
-      </c>
-      <c r="C101">
-        <v>72.97363148867436</v>
-      </c>
-      <c r="D101">
-        <v>360.2716314886744</v>
-      </c>
-      <c r="E101">
-        <v>287.298</v>
-      </c>
-      <c r="F101">
-        <v>287.298</v>
-      </c>
-      <c r="G101">
-        <v>0</v>
-      </c>
-      <c r="H101">
-        <v>290.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>67.7</v>
-      </c>
-      <c r="K101">
-        <v>5.5</v>
-      </c>
-      <c r="L101">
-        <v>62.2</v>
-      </c>
-      <c r="M101">
-        <v>17.6113674</v>
-      </c>
-      <c r="N101">
-        <v>44.5886326</v>
-      </c>
-      <c r="O101">
-        <v>13.37658978</v>
-      </c>
-      <c r="P101">
-        <v>31.21204282</v>
-      </c>
-      <c r="Q101">
-        <v>36.71204282</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.664577337943643</v>
-      </c>
-      <c r="T101">
-        <v>39.17660221728335</v>
-      </c>
-      <c r="U101">
-        <v>0.0613</v>
-      </c>
-      <c r="V101">
-        <v>0.3</v>
-      </c>
-      <c r="W101">
-        <v>0.04291</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ba1/BB+</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>3.531809801435407</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
